--- a/ECON251/Tutorial/T01/Tutorial assignment 1 data _KOH EE HUI JOSEPH.xlsx
+++ b/ECON251/Tutorial/T01/Tutorial assignment 1 data _KOH EE HUI JOSEPH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ECON251\Tutorial\T01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC163BE-8592-4021-80EC-00B42B137FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A1725-9B86-4B5A-BA77-C23DA96FA98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="729" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="187">
   <si>
     <t>Development relevance</t>
   </si>
@@ -941,7 +941,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="107">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1150,9 +1150,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1202,6 +1199,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -16547,7 +16552,7 @@
       <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="96" t="s">
+      <c r="I1" s="95" t="s">
         <v>182</v>
       </c>
       <c r="J1" s="2" t="s">
@@ -21194,13 +21199,13 @@
     <col min="17" max="17" width="17.85546875" style="66" customWidth="1"/>
     <col min="18" max="18" width="6.140625" style="24" customWidth="1"/>
     <col min="19" max="19" width="13.28515625" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" style="100" customWidth="1"/>
+    <col min="20" max="20" width="13.28515625" style="99" customWidth="1"/>
     <col min="21" max="21" width="4.42578125" style="22" customWidth="1"/>
     <col min="22" max="22" width="13.28515625" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="30" style="50" customWidth="1"/>
     <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="100" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="99" customWidth="1"/>
     <col min="30" max="30" width="3.7109375" style="22" customWidth="1"/>
     <col min="32" max="32" width="9" style="20" customWidth="1"/>
   </cols>
@@ -21254,10 +21259,10 @@
         <v>181</v>
       </c>
       <c r="R1" s="30"/>
-      <c r="S1" s="97" t="s">
+      <c r="S1" s="96" t="s">
         <v>182</v>
       </c>
-      <c r="T1" s="98" t="s">
+      <c r="T1" s="97" t="s">
         <v>153</v>
       </c>
       <c r="U1" s="28"/>
@@ -21279,7 +21284,7 @@
       <c r="AA1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="101" t="s">
+      <c r="AB1" s="100" t="s">
         <v>168</v>
       </c>
       <c r="AC1" s="27" t="s">
@@ -21339,7 +21344,7 @@
       <c r="S2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="T2" s="99" t="s">
+      <c r="T2" s="98" t="s">
         <v>151</v>
       </c>
       <c r="U2" s="25"/>
@@ -21351,7 +21356,7 @@
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
       <c r="AA2" s="55"/>
-      <c r="AB2" s="102" t="s">
+      <c r="AB2" s="101" t="s">
         <v>151</v>
       </c>
       <c r="AC2" s="55"/>
@@ -21440,7 +21445,7 @@
       <c r="AA3">
         <v>30.430790153344098</v>
       </c>
-      <c r="AB3" s="103"/>
+      <c r="AB3" s="102"/>
       <c r="AC3">
         <v>64.1185656445506</v>
       </c>
@@ -21535,7 +21540,7 @@
       <c r="AA4">
         <v>29.651708418805299</v>
       </c>
-      <c r="AB4" s="100">
+      <c r="AB4" s="99">
         <f>M4-M3</f>
         <v>-0.57506237805308569</v>
       </c>
@@ -21636,7 +21641,7 @@
       <c r="AA5">
         <v>28.789947213679</v>
       </c>
-      <c r="AB5" s="100">
+      <c r="AB5" s="99">
         <f t="shared" ref="AB5:AB27" si="7">M5-M4</f>
         <v>-0.63775574906170962</v>
       </c>
@@ -21737,7 +21742,7 @@
       <c r="AA6">
         <v>28.721289647208501</v>
       </c>
-      <c r="AB6" s="100">
+      <c r="AB6" s="99">
         <f t="shared" si="7"/>
         <v>0.951399925894576</v>
       </c>
@@ -21838,7 +21843,7 @@
       <c r="AA7">
         <v>27.822772205516198</v>
       </c>
-      <c r="AB7" s="100">
+      <c r="AB7" s="99">
         <f t="shared" si="7"/>
         <v>0.39140629627848489</v>
       </c>
@@ -21939,7 +21944,7 @@
       <c r="AA8">
         <v>27.392084976308698</v>
       </c>
-      <c r="AB8" s="100">
+      <c r="AB8" s="99">
         <f t="shared" si="7"/>
         <v>0.28258790508910614</v>
       </c>
@@ -22040,7 +22045,7 @@
       <c r="AA9">
         <v>27.495246318005801</v>
       </c>
-      <c r="AB9" s="100">
+      <c r="AB9" s="99">
         <f t="shared" si="7"/>
         <v>2.2879012433650925E-2</v>
       </c>
@@ -22141,7 +22146,7 @@
       <c r="AA10">
         <v>27.290260731194699</v>
       </c>
-      <c r="AB10" s="100">
+      <c r="AB10" s="99">
         <f t="shared" si="7"/>
         <v>3.7106879855957731E-2</v>
       </c>
@@ -22242,7 +22247,7 @@
       <c r="AA11">
         <v>26.771635935298701</v>
       </c>
-      <c r="AB11" s="100">
+      <c r="AB11" s="99">
         <f t="shared" si="7"/>
         <v>-0.86910502118931809</v>
       </c>
@@ -22343,7 +22348,7 @@
       <c r="AA12">
         <v>26.094293020591699</v>
       </c>
-      <c r="AB12" s="100">
+      <c r="AB12" s="99">
         <f t="shared" si="7"/>
         <v>-1.1181954737153901</v>
       </c>
@@ -22444,7 +22449,7 @@
       <c r="AA13">
         <v>25.519323328132199</v>
       </c>
-      <c r="AB13" s="100">
+      <c r="AB13" s="99">
         <f t="shared" si="7"/>
         <v>1.1193967097979134</v>
       </c>
@@ -22545,7 +22550,7 @@
       <c r="AA14">
         <v>25.430185651152598</v>
       </c>
-      <c r="AB14" s="100">
+      <c r="AB14" s="99">
         <f t="shared" si="7"/>
         <v>0.3286594751730233</v>
       </c>
@@ -22646,7 +22651,7 @@
       <c r="AA15">
         <v>25.311193891919999</v>
       </c>
-      <c r="AB15" s="100">
+      <c r="AB15" s="99">
         <f t="shared" si="7"/>
         <v>-0.18490803263721761</v>
       </c>
@@ -22747,7 +22752,7 @@
       <c r="AA16">
         <v>25.1886060017838</v>
       </c>
-      <c r="AB16" s="100">
+      <c r="AB16" s="99">
         <f t="shared" si="7"/>
         <v>0.95994610606551145</v>
       </c>
@@ -22830,7 +22835,7 @@
       <c r="S17">
         <v>62.833488464355497</v>
       </c>
-      <c r="T17" s="100">
+      <c r="T17" s="99">
         <f>S17-S16</f>
         <v>0.19121932983399859</v>
       </c>
@@ -22852,7 +22857,7 @@
       <c r="AA17">
         <v>25.125568425648702</v>
       </c>
-      <c r="AB17" s="100">
+      <c r="AB17" s="99">
         <f t="shared" si="7"/>
         <v>9.9890258511795227E-2</v>
       </c>
@@ -22935,7 +22940,7 @@
       <c r="S18">
         <v>62.4498481750488</v>
       </c>
-      <c r="T18" s="100">
+      <c r="T18" s="99">
         <f t="shared" ref="T18:T26" si="9">S18-S17</f>
         <v>-0.38364028930669747</v>
       </c>
@@ -22957,7 +22962,7 @@
       <c r="AA18">
         <v>24.90449732946</v>
       </c>
-      <c r="AB18" s="100">
+      <c r="AB18" s="99">
         <f t="shared" si="7"/>
         <v>-0.46316764407036926</v>
       </c>
@@ -23040,7 +23045,7 @@
       <c r="S19">
         <v>62.4975395202637</v>
       </c>
-      <c r="T19" s="100">
+      <c r="T19" s="99">
         <f t="shared" si="9"/>
         <v>4.7691345214900593E-2</v>
       </c>
@@ -23062,7 +23067,7 @@
       <c r="AA19">
         <v>24.594734051284</v>
       </c>
-      <c r="AB19" s="100">
+      <c r="AB19" s="99">
         <f t="shared" si="7"/>
         <v>0.82616306112364746</v>
       </c>
@@ -23145,7 +23150,7 @@
       <c r="S20">
         <v>63.287540435791001</v>
       </c>
-      <c r="T20" s="100">
+      <c r="T20" s="99">
         <f t="shared" si="9"/>
         <v>0.79000091552730112</v>
       </c>
@@ -23167,7 +23172,7 @@
       <c r="AA20">
         <v>24.581906234304501</v>
       </c>
-      <c r="AB20" s="100">
+      <c r="AB20" s="99">
         <f t="shared" si="7"/>
         <v>-3.4423707363241407E-2</v>
       </c>
@@ -23250,7 +23255,7 @@
       <c r="S21">
         <v>62.605850219726598</v>
       </c>
-      <c r="T21" s="100">
+      <c r="T21" s="99">
         <f t="shared" si="9"/>
         <v>-0.68169021606440339</v>
       </c>
@@ -23272,7 +23277,7 @@
       <c r="AA21">
         <v>24.4484966180265</v>
       </c>
-      <c r="AB21" s="100">
+      <c r="AB21" s="99">
         <f t="shared" si="7"/>
         <v>0.89887603732049737</v>
       </c>
@@ -23355,7 +23360,7 @@
       <c r="S22">
         <v>62.400840759277301</v>
       </c>
-      <c r="T22" s="100">
+      <c r="T22" s="99">
         <f t="shared" si="9"/>
         <v>-0.20500946044929691</v>
       </c>
@@ -23377,7 +23382,7 @@
       <c r="AA22">
         <v>24.225756536984001</v>
       </c>
-      <c r="AB22" s="100">
+      <c r="AB22" s="99">
         <f t="shared" si="7"/>
         <v>-0.99913676686988651</v>
       </c>
@@ -23460,7 +23465,7 @@
       <c r="S23">
         <v>62.298740386962898</v>
       </c>
-      <c r="T23" s="100">
+      <c r="T23" s="99">
         <f t="shared" si="9"/>
         <v>-0.10210037231440339</v>
       </c>
@@ -23482,7 +23487,7 @@
       <c r="AA23">
         <v>23.931926038039101</v>
       </c>
-      <c r="AB23" s="100">
+      <c r="AB23" s="99">
         <f t="shared" si="7"/>
         <v>-1.7306405438873615</v>
       </c>
@@ -23565,7 +23570,7 @@
       <c r="S24">
         <v>62.041248321533203</v>
       </c>
-      <c r="T24" s="100">
+      <c r="T24" s="99">
         <f t="shared" si="9"/>
         <v>-0.25749206542969461</v>
       </c>
@@ -23587,7 +23592,7 @@
       <c r="AA24">
         <v>23.697096196032799</v>
       </c>
-      <c r="AB24" s="100">
+      <c r="AB24" s="99">
         <f t="shared" si="7"/>
         <v>0.60247937174166499</v>
       </c>
@@ -23670,7 +23675,7 @@
       <c r="S25">
         <v>63.375228881835902</v>
       </c>
-      <c r="T25" s="100">
+      <c r="T25" s="99">
         <f t="shared" si="9"/>
         <v>1.3339805603026988</v>
       </c>
@@ -23692,7 +23697,7 @@
       <c r="AA25">
         <v>23.622131923842399</v>
       </c>
-      <c r="AB25" s="100">
+      <c r="AB25" s="99">
         <f t="shared" si="7"/>
         <v>0.7855573073249027</v>
       </c>
@@ -23772,7 +23777,7 @@
       <c r="S26">
         <v>64.490760803222699</v>
       </c>
-      <c r="T26" s="100">
+      <c r="T26" s="99">
         <f t="shared" si="9"/>
         <v>1.1155319213867969</v>
       </c>
@@ -23794,7 +23799,7 @@
       <c r="AA26">
         <v>23.708847999943401</v>
       </c>
-      <c r="AB26" s="100">
+      <c r="AB26" s="99">
         <f t="shared" si="7"/>
         <v>-0.29382019316788272</v>
       </c>
@@ -23892,7 +23897,7 @@
       <c r="AA27">
         <v>23.344843518808201</v>
       </c>
-      <c r="AB27" s="100">
+      <c r="AB27" s="99">
         <f t="shared" si="7"/>
         <v>0.14322788395289981</v>
       </c>
@@ -23931,18 +23936,18 @@
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="60"/>
-      <c r="N28" s="95">
+      <c r="N28" s="94">
         <f>AVERAGE(N3:N27)</f>
         <v>68028.140254514699</v>
       </c>
       <c r="O28" s="60"/>
-      <c r="P28" s="95">
+      <c r="P28" s="94">
         <f>AVERAGE(P3:P27)</f>
         <v>18374.506309445525</v>
       </c>
       <c r="Q28" s="70"/>
       <c r="R28" s="24"/>
-      <c r="T28" s="100"/>
+      <c r="T28" s="99"/>
       <c r="U28" s="22"/>
       <c r="V28" s="15">
         <f>AVERAGE(V3:V27)</f>
@@ -23964,7 +23969,7 @@
         <f>AVERAGE(AA3:AA27)</f>
         <v>25.923805694612593</v>
       </c>
-      <c r="AB28" s="100"/>
+      <c r="AB28" s="99"/>
       <c r="AC28" s="15">
         <f>AVERAGE(AC3:AC27)</f>
         <v>69.981175043331774</v>
@@ -24152,6 +24157,7 @@
     <col min="3" max="3" width="31.140625" customWidth="1"/>
     <col min="4" max="4" width="16.28515625" customWidth="1"/>
     <col min="6" max="6" width="44.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.5703125" customWidth="1"/>
     <col min="8" max="8" width="17.140625" customWidth="1"/>
     <col min="9" max="9" width="10.5703125" customWidth="1"/>
   </cols>
@@ -24256,7 +24262,7 @@
       <c r="F6" t="s">
         <v>118</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="37">
         <v>0.24890208406245068</v>
       </c>
     </row>
@@ -24316,7 +24322,7 @@
       <c r="F9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="38">
         <v>25</v>
       </c>
     </row>
@@ -24493,7 +24499,7 @@
         <v>65843453</v>
       </c>
       <c r="F17" s="10"/>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="103" t="s">
         <v>132</v>
       </c>
       <c r="H17" s="10" t="s">
@@ -24502,7 +24508,7 @@
       <c r="I17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="J17" s="103" t="s">
         <v>134</v>
       </c>
       <c r="K17" s="10" t="s">
@@ -24534,7 +24540,7 @@
       <c r="F18" t="s">
         <v>126</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="37">
         <v>-1669481669160.6504</v>
       </c>
       <c r="H18">
@@ -24543,7 +24549,7 @@
       <c r="I18">
         <v>-0.61579381020356161</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="37">
         <v>0.54434953425183896</v>
       </c>
       <c r="K18">
@@ -24575,7 +24581,7 @@
       <c r="F19" t="s">
         <v>173</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="37">
         <v>0.12492885422063238</v>
       </c>
       <c r="H19">
@@ -24616,7 +24622,7 @@
       <c r="F20" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="38">
         <v>88098.975250276853</v>
       </c>
       <c r="H20" s="9">
@@ -25138,10 +25144,10 @@
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="77">
+      <c r="A17" s="105">
         <v>2014</v>
       </c>
-      <c r="B17" s="78">
+      <c r="B17" s="77">
         <v>0.90591548606586514</v>
       </c>
       <c r="C17" s="78">
@@ -25154,7 +25160,7 @@
         <f>D17-D16</f>
         <v>9.9890258511795227E-2</v>
       </c>
-      <c r="F17" s="86">
+      <c r="F17" s="85">
         <v>4.8581973539594016E-3</v>
       </c>
       <c r="H17" s="10"/>
@@ -25184,23 +25190,23 @@
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="80">
+      <c r="A18" s="105">
         <v>2015</v>
       </c>
-      <c r="B18" s="81">
+      <c r="B18" s="80">
         <v>1.7999773578347487</v>
       </c>
-      <c r="C18" s="81">
+      <c r="C18" s="104">
         <v>2.8541342380652424</v>
       </c>
-      <c r="D18" s="82">
+      <c r="D18" s="106">
         <v>0.34507827037292893</v>
       </c>
-      <c r="E18" s="81">
+      <c r="E18" s="104">
         <f t="shared" ref="E18:E26" si="0">D18-D17</f>
         <v>-0.46316764407036926</v>
       </c>
-      <c r="F18" s="87">
+      <c r="F18" s="86">
         <v>8.9782830654430018E-4</v>
       </c>
       <c r="H18" t="s">
@@ -25232,23 +25238,23 @@
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="80">
+      <c r="A19" s="105">
         <v>2016</v>
       </c>
-      <c r="B19" s="81">
+      <c r="B19" s="80">
         <v>0.70498649511125677</v>
       </c>
-      <c r="C19" s="81">
+      <c r="C19" s="104">
         <v>0.65911104198646342</v>
       </c>
-      <c r="D19" s="82">
+      <c r="D19" s="106">
         <v>1.1712413314965764</v>
       </c>
-      <c r="E19" s="81">
+      <c r="E19" s="104">
         <f t="shared" si="0"/>
         <v>0.82616306112364746</v>
       </c>
-      <c r="F19" s="87">
+      <c r="F19" s="86">
         <v>-3.7918470149631012E-3</v>
       </c>
       <c r="H19" t="s">
@@ -25280,23 +25286,23 @@
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="80">
+      <c r="A20" s="105">
         <v>2017</v>
       </c>
-      <c r="B20" s="81">
+      <c r="B20" s="80">
         <v>1.6234506224544134</v>
       </c>
-      <c r="C20" s="81">
+      <c r="C20" s="104">
         <v>1.6097468891013165</v>
       </c>
-      <c r="D20" s="82">
+      <c r="D20" s="106">
         <v>1.136817624133335</v>
       </c>
-      <c r="E20" s="81">
+      <c r="E20" s="104">
         <f t="shared" si="0"/>
         <v>-3.4423707363241407E-2</v>
       </c>
-      <c r="F20" s="87">
+      <c r="F20" s="86">
         <v>1.3269004203637198E-2</v>
       </c>
       <c r="H20" t="s">
@@ -25328,23 +25334,23 @@
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="80">
+      <c r="A21" s="105">
         <v>2018</v>
       </c>
-      <c r="B21" s="81">
+      <c r="B21" s="80">
         <v>0.83414384596558477</v>
       </c>
-      <c r="C21" s="81">
+      <c r="C21" s="104">
         <v>1.2789260829120224</v>
       </c>
-      <c r="D21" s="82">
+      <c r="D21" s="106">
         <v>2.0356936614538323</v>
       </c>
-      <c r="E21" s="81">
+      <c r="E21" s="104">
         <f t="shared" si="0"/>
         <v>0.89887603732049737</v>
       </c>
-      <c r="F21" s="87">
+      <c r="F21" s="86">
         <v>-1.6904672173859991E-3</v>
       </c>
       <c r="H21" t="s">
@@ -25376,23 +25382,23 @@
       </c>
     </row>
     <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="80">
+      <c r="A22" s="105">
         <v>2019</v>
       </c>
-      <c r="B22" s="81">
+      <c r="B22" s="80">
         <v>-0.30849692114325933</v>
       </c>
-      <c r="C22" s="81">
+      <c r="C22" s="104">
         <v>1.6606576436665677</v>
       </c>
-      <c r="D22" s="82">
+      <c r="D22" s="106">
         <v>1.0365568945839458</v>
       </c>
-      <c r="E22" s="81">
+      <c r="E22" s="104">
         <f t="shared" si="0"/>
         <v>-0.99913676686988651</v>
       </c>
-      <c r="F22" s="87">
+      <c r="F22" s="86">
         <v>5.6473259349969503E-2</v>
       </c>
       <c r="H22" s="9" t="s">
@@ -25424,44 +25430,44 @@
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="80">
+      <c r="A23" s="105">
         <v>2020</v>
       </c>
-      <c r="B23" s="81">
+      <c r="B23" s="80">
         <v>-4.2832794267557261</v>
       </c>
-      <c r="C23" s="81">
+      <c r="C23" s="104">
         <v>-3.45000520130327</v>
       </c>
-      <c r="D23" s="82">
+      <c r="D23" s="106">
         <v>-0.6940836493034156</v>
       </c>
-      <c r="E23" s="81">
+      <c r="E23" s="104">
         <f t="shared" si="0"/>
         <v>-1.7306405438873615</v>
       </c>
-      <c r="F23" s="87">
+      <c r="F23" s="86">
         <v>3.768539613590402E-3</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="83">
+      <c r="A24" s="105">
         <v>2021</v>
       </c>
-      <c r="B24" s="84">
+      <c r="B24" s="82">
         <v>3.5641953147447509</v>
       </c>
-      <c r="C24" s="84">
+      <c r="C24" s="83">
         <v>1.039988028532008</v>
       </c>
-      <c r="D24" s="85">
+      <c r="D24" s="84">
         <v>-9.1604277561750574E-2</v>
       </c>
-      <c r="E24" s="84">
+      <c r="E24" s="83">
         <f t="shared" si="0"/>
         <v>0.60247937174166499</v>
       </c>
-      <c r="F24" s="88">
+      <c r="F24" s="87">
         <v>-4.9692738437576101E-2</v>
       </c>
     </row>
@@ -25526,600 +25532,679 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07465A97-DC41-4842-AB21-460AF263DB7D}">
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:O27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.5703125" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" customWidth="1"/>
-    <col min="3" max="3" width="12.28515625" customWidth="1"/>
-    <col min="4" max="4" width="19.7109375" customWidth="1"/>
-    <col min="6" max="6" width="46.85546875" customWidth="1"/>
-    <col min="11" max="11" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.7109375" customWidth="1"/>
+    <col min="7" max="7" width="46.85546875" customWidth="1"/>
+    <col min="12" max="12" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="120" x14ac:dyDescent="0.25">
-      <c r="A1" s="69" t="s">
+    <row r="1" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="69" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="69" t="s">
+      <c r="C1" s="69" t="s">
         <v>181</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="D1" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="E1" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="76" t="s">
+      <c r="G1" s="76" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="90" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+    <row r="2" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="18"/>
+      <c r="B2" s="65" t="s">
         <v>142</v>
       </c>
-      <c r="B2" s="68" t="s">
+      <c r="C2" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="D2" s="55"/>
-      <c r="F2" s="43" t="s">
+      <c r="E2" s="55"/>
+      <c r="G2" s="43" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62"/>
+    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>2000</v>
+      </c>
       <c r="B3" s="62"/>
-      <c r="C3" s="20"/>
-      <c r="D3">
+      <c r="C3" s="62"/>
+      <c r="D3" s="20"/>
+      <c r="E3">
         <v>5.9527340709045689</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="66">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2001</v>
+      </c>
+      <c r="B4" s="66">
         <v>0.86464317201881413</v>
       </c>
-      <c r="B4" s="66">
+      <c r="C4" s="66">
         <v>-0.93019454533183632</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4">
+      <c r="D4" s="20"/>
+      <c r="E4">
         <v>-3.8993064419592969</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="G4" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="G4" s="11"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="66">
+      <c r="H4" s="11"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2002</v>
+      </c>
+      <c r="B5" s="66">
         <v>1.3137402115803731</v>
       </c>
-      <c r="B5" s="66">
+      <c r="C5" s="66">
         <v>-3.2380649204662029</v>
       </c>
-      <c r="C5" s="20"/>
-      <c r="D5">
+      <c r="D5" s="20"/>
+      <c r="E5">
         <v>-2.021784916640712</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>117</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <v>0.87250112639139465</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="66">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>2003</v>
+      </c>
+      <c r="B6" s="66">
         <v>1.6458300588631878</v>
       </c>
-      <c r="B6" s="66">
+      <c r="C6" s="66">
         <v>-0.72907516487515189</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6">
+      <c r="D6" s="20"/>
+      <c r="E6">
         <v>3.6892235030364589</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>118</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="37">
         <v>0.76125821555425244</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="66">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>2004</v>
+      </c>
+      <c r="B7" s="66">
         <v>1.9803858762976283</v>
       </c>
-      <c r="B7" s="66">
+      <c r="C7" s="66">
         <v>9.3201215593103209E-2</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7">
+      <c r="D7" s="20"/>
+      <c r="E7">
         <v>5.2725079432044453</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>119</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <v>0.64188732333137866</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="66">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>2005</v>
+      </c>
+      <c r="B8" s="66">
         <v>1.4298062996948859</v>
       </c>
-      <c r="B8" s="66">
+      <c r="C8" s="66">
         <v>2.4537738050092481</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8">
+      <c r="D8" s="20"/>
+      <c r="E8">
         <v>3.6194835541111843</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>120</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <v>1.1401461141028588</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="66">
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>2006</v>
+      </c>
+      <c r="B9" s="66">
         <v>1.1060371241084361</v>
       </c>
-      <c r="B9" s="66">
+      <c r="C9" s="66">
         <v>0.30008532136144822</v>
       </c>
-      <c r="C9" s="20"/>
-      <c r="D9">
+      <c r="D9" s="20"/>
+      <c r="E9">
         <v>3.9753848633023949</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G9" s="9">
+      <c r="H9" s="38">
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="66">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>2007</v>
+      </c>
+      <c r="B10" s="66">
         <v>1.2499106348688975</v>
       </c>
-      <c r="B10" s="66">
+      <c r="C10" s="66">
         <v>-1.5598376214867455</v>
       </c>
-      <c r="C10" s="20"/>
-      <c r="D10">
+      <c r="D10" s="20"/>
+      <c r="E10">
         <v>5.4347531277969949</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66">
+    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>2008</v>
+      </c>
+      <c r="B11" s="66">
         <v>-0.77314481744796404</v>
       </c>
-      <c r="B11" s="66">
+      <c r="C11" s="66">
         <v>-3.2920040222025904</v>
       </c>
-      <c r="C11" s="20"/>
-      <c r="D11">
+      <c r="D11" s="20"/>
+      <c r="E11">
         <v>0.21369602246103625</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="66">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>2009</v>
+      </c>
+      <c r="B12" s="66">
         <v>-4.4892022148193922</v>
       </c>
-      <c r="B12" s="66">
+      <c r="C12" s="66">
         <v>-9.1025998784664353</v>
       </c>
-      <c r="C12" s="20"/>
-      <c r="D12">
+      <c r="D12" s="20"/>
+      <c r="E12">
         <v>-17.167772289390797</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="10"/>
+      <c r="H12" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="I12" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="I12" s="10" t="s">
+      <c r="J12" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="J12" s="10" t="s">
+      <c r="K12" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="L12" s="10" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="66">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>2010</v>
+      </c>
+      <c r="B13" s="66">
         <v>4.5497849909879697</v>
       </c>
-      <c r="B13" s="66">
+      <c r="C13" s="66">
         <v>-1.1987277173142665</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13">
+      <c r="D13" s="20"/>
+      <c r="E13">
         <v>16.886878489115944</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>123</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <v>3</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <v>24.870002571948461</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>8.2900008573161532</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>6.3772516178645136</v>
       </c>
-      <c r="K13">
+      <c r="L13">
         <v>2.6960101617431578E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="66">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>2011</v>
+      </c>
+      <c r="B14" s="66">
         <v>-0.13376463332428132</v>
       </c>
-      <c r="B14" s="66">
+      <c r="C14" s="66">
         <v>1.5034484451759154</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14">
+      <c r="D14" s="20"/>
+      <c r="E14">
         <v>-3.1910773685471412</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>124</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <v>6</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <v>7.7995989690230934</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>1.299933161503849</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="66">
+    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>2012</v>
+      </c>
+      <c r="B15" s="66">
         <v>1.9053185795370033</v>
       </c>
-      <c r="B15" s="66">
+      <c r="C15" s="66">
         <v>3.6936688947658212</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15">
+      <c r="D15" s="20"/>
+      <c r="E15">
         <v>2.0336463223787291</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="9">
+      <c r="H15" s="9">
         <v>9</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <v>32.669601540971556</v>
       </c>
-      <c r="I15" s="9"/>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66">
+      <c r="L15" s="9"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>2013</v>
+      </c>
+      <c r="B16" s="66">
         <v>1.2798549531130496</v>
       </c>
-      <c r="B16" s="66">
+      <c r="C16" s="66">
         <v>2.7465999616935024</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16">
+      <c r="D16" s="20"/>
+      <c r="E16">
         <v>-1.4564912307609745</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="89">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2014</v>
+      </c>
+      <c r="B17" s="88">
         <v>9.6886490521281607E-2</v>
       </c>
-      <c r="B17" s="90">
+      <c r="C17" s="89">
         <v>3.2307540889096353</v>
       </c>
-      <c r="C17" s="78">
-        <f>B17-B16</f>
+      <c r="D17" s="78">
+        <f>C17-C16</f>
         <v>0.48415412721613293</v>
       </c>
-      <c r="D17" s="86">
+      <c r="E17" s="85">
         <v>2.9031184885573822</v>
       </c>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10" t="s">
+      <c r="G17" s="10"/>
+      <c r="H17" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="I17" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="I17" s="10" t="s">
+      <c r="J17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="10" t="s">
+      <c r="K17" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="L17" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="M17" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="M17" s="10" t="s">
+      <c r="N17" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="N17" s="10" t="s">
+      <c r="O17" s="10" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="91">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2015</v>
+      </c>
+      <c r="B18" s="90">
         <v>1.4498958120713157</v>
       </c>
-      <c r="B18" s="92">
+      <c r="C18" s="91">
         <v>2.5004275356005334</v>
       </c>
-      <c r="C18" s="81">
-        <f t="shared" ref="C18:C26" si="0">B18-B17</f>
+      <c r="D18" s="81">
+        <f t="shared" ref="D18:D26" si="0">C18-C17</f>
         <v>-0.7303265533091019</v>
       </c>
-      <c r="D18" s="87">
+      <c r="E18" s="86">
         <v>2.0940745404323167</v>
       </c>
-      <c r="F18" t="s">
+      <c r="G18" t="s">
         <v>126</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <v>-0.5035750489208316</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <v>0.42524554601217013</v>
       </c>
-      <c r="I18">
+      <c r="J18">
         <v>-1.1841982911830893</v>
       </c>
-      <c r="J18">
+      <c r="K18">
         <v>0.28111524658666631</v>
       </c>
-      <c r="K18">
+      <c r="L18">
         <v>-1.5441134151046243</v>
       </c>
-      <c r="L18">
+      <c r="M18">
         <v>0.53696331726296098</v>
       </c>
-      <c r="M18">
+      <c r="N18">
         <v>-1.5441134151046243</v>
       </c>
-      <c r="N18">
+      <c r="O18">
         <v>0.53696331726296098</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="91">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="90">
         <v>-0.46085708769510181</v>
       </c>
-      <c r="B19" s="92">
+      <c r="C19" s="91">
         <v>-0.50620144891972196</v>
       </c>
-      <c r="C19" s="81">
+      <c r="D19" s="81">
         <f t="shared" si="0"/>
         <v>-3.0066289845202556</v>
       </c>
-      <c r="D19" s="87">
+      <c r="E19" s="86">
         <v>0.86648629529422294</v>
       </c>
-      <c r="F19" t="s">
+      <c r="G19" t="s">
         <v>173</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <v>0.21462761453424245</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <v>0.28631741219953466</v>
       </c>
-      <c r="I19">
+      <c r="J19">
         <v>0.74961425812506444</v>
       </c>
-      <c r="J19">
+      <c r="K19">
         <v>0.48183362661814588</v>
       </c>
-      <c r="K19">
+      <c r="L19">
         <v>-0.48596585456595826</v>
       </c>
-      <c r="L19">
+      <c r="M19">
         <v>0.91522108363444321</v>
       </c>
-      <c r="M19">
+      <c r="N19">
         <v>-0.48596585456595826</v>
       </c>
-      <c r="N19">
+      <c r="O19">
         <v>0.91522108363444321</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="91">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>2017</v>
+      </c>
+      <c r="B20" s="90">
         <v>0.48116305194575515</v>
       </c>
-      <c r="B20" s="92">
+      <c r="C20" s="91">
         <v>0.46761335394750919</v>
       </c>
-      <c r="C20" s="81">
+      <c r="D20" s="81">
         <f t="shared" si="0"/>
         <v>0.9738148028672311</v>
       </c>
-      <c r="D20" s="87">
+      <c r="E20" s="86">
         <v>4.2332505930130964</v>
       </c>
-      <c r="F20" t="s">
+      <c r="G20" t="s">
         <v>174</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <v>0.24449531397220281</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <v>0.2230286071702785</v>
       </c>
-      <c r="I20">
+      <c r="J20">
         <v>1.0962509118192845</v>
       </c>
-      <c r="J20">
+      <c r="K20">
         <v>0.31500788667642005</v>
       </c>
-      <c r="K20">
+      <c r="L20">
         <v>-0.30123602805710759</v>
       </c>
-      <c r="L20">
+      <c r="M20">
         <v>0.79022665600151321</v>
       </c>
-      <c r="M20">
+      <c r="N20">
         <v>-0.30123602805710759</v>
       </c>
-      <c r="N20">
+      <c r="O20">
         <v>0.79022665600151321</v>
       </c>
     </row>
-    <row r="21" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="91">
+    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>2018</v>
+      </c>
+      <c r="B21" s="90">
         <v>-1.177577936084699</v>
       </c>
-      <c r="B21" s="92">
+      <c r="C21" s="91">
         <v>-0.74166946034856995</v>
       </c>
-      <c r="C21" s="81">
+      <c r="D21" s="81">
         <f t="shared" si="0"/>
         <v>-1.2092828142960792</v>
       </c>
-      <c r="D21" s="87">
+      <c r="E21" s="86">
         <v>3.7499108296410242</v>
       </c>
-      <c r="F21" s="9" t="s">
+      <c r="G21" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="G21" s="9">
+      <c r="H21" s="9">
         <v>0.29974237268679343</v>
       </c>
-      <c r="H21" s="9">
+      <c r="I21" s="9">
         <v>0.13329959186617352</v>
       </c>
-      <c r="I21" s="9">
+      <c r="J21" s="9">
         <v>2.2486368374459884</v>
       </c>
-      <c r="J21" s="9">
+      <c r="K21" s="9">
         <v>6.5563928894571702E-2</v>
       </c>
-      <c r="K21" s="9">
+      <c r="L21" s="9">
         <v>-2.6429978403334164E-2</v>
       </c>
-      <c r="L21" s="9">
+      <c r="M21" s="9">
         <v>0.62591472377692103</v>
       </c>
-      <c r="M21" s="9">
+      <c r="N21" s="9">
         <v>-2.6429978403334164E-2</v>
       </c>
-      <c r="N21" s="9">
+      <c r="O21" s="9">
         <v>0.62591472377692103</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="91">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="90">
         <v>-1.3312546043414482</v>
       </c>
-      <c r="B22" s="92">
+      <c r="C22" s="91">
         <v>0.61769795830808505</v>
       </c>
-      <c r="C22" s="81">
+      <c r="D22" s="81">
         <f t="shared" si="0"/>
         <v>1.3593674186566549</v>
       </c>
-      <c r="D22" s="87">
+      <c r="E22" s="86">
         <v>-0.88808077103949756</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="91">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>2020</v>
+      </c>
+      <c r="B23" s="90">
         <v>-3.6142819172798877</v>
       </c>
-      <c r="B23" s="92">
+      <c r="C23" s="91">
         <v>-2.7751836479383445</v>
       </c>
-      <c r="C23" s="81">
+      <c r="D23" s="81">
         <f t="shared" si="0"/>
         <v>-3.3928816062464295</v>
       </c>
-      <c r="D23" s="87">
+      <c r="E23" s="86">
         <v>-6.1172472387425643</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="91">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>2021</v>
+      </c>
+      <c r="B24" s="90">
         <v>3.6591515316319545</v>
       </c>
-      <c r="B24" s="92">
+      <c r="C24" s="91">
         <v>1.1326298434793314</v>
       </c>
-      <c r="C24" s="81">
+      <c r="D24" s="81">
         <f t="shared" si="0"/>
         <v>3.9078134914176759</v>
       </c>
-      <c r="D24" s="87">
+      <c r="E24" s="86">
         <v>6.2091300540067209</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="91">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25">
+        <v>2022</v>
+      </c>
+      <c r="B25" s="90">
         <v>0.63329967449560209</v>
       </c>
-      <c r="B25" s="92">
+      <c r="C25" s="91">
         <v>-0.22334416663875237</v>
       </c>
-      <c r="C25" s="81">
+      <c r="D25" s="81">
         <f t="shared" si="0"/>
         <v>-1.3559740101180837</v>
       </c>
-      <c r="D25" s="87">
+      <c r="E25" s="86">
         <v>2.4197275090146064</v>
       </c>
     </row>
-    <row r="26" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="93">
+    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>2023</v>
+      </c>
+      <c r="B26" s="92">
         <v>0.3193745457253746</v>
       </c>
-      <c r="B26" s="94">
+      <c r="C26" s="93">
         <v>1.5075004155496978</v>
       </c>
-      <c r="C26" s="84">
+      <c r="D26" s="83">
         <f t="shared" si="0"/>
         <v>1.7308445821884502</v>
       </c>
-      <c r="D26" s="88">
+      <c r="E26" s="87">
         <v>-1.2039654711156373</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A27" s="66">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>2024</v>
+      </c>
+      <c r="B27" s="66">
         <v>-0.77921102992308133</v>
       </c>
-      <c r="B27" s="66">
+      <c r="C27" s="66">
         <v>-1.1032122677168328</v>
       </c>
-      <c r="C27" s="20"/>
-      <c r="D27">
+      <c r="D27" s="20"/>
+      <c r="E27">
         <v>-5.7836044198951271</v>
       </c>
     </row>

--- a/ECON251/Tutorial/T01/Tutorial assignment 1 data _KOH EE HUI JOSEPH.xlsx
+++ b/ECON251/Tutorial/T01/Tutorial assignment 1 data _KOH EE HUI JOSEPH.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10703"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ECON251\Tutorial\T01\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ECON251/Tutorial/T01/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B5A1725-9B86-4B5A-BA77-C23DA96FA98E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AB29A5E-93BA-9C4D-8F93-C6E8CF57B9CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="33600" windowHeight="18800" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="730" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="789" uniqueCount="215">
   <si>
     <t>Development relevance</t>
   </si>
@@ -595,18 +595,6 @@
     <t>h</t>
   </si>
   <si>
-    <t>X Variable 1</t>
-  </si>
-  <si>
-    <t>X Variable 2</t>
-  </si>
-  <si>
-    <t>X Variable 3</t>
-  </si>
-  <si>
-    <t>X Variable 4</t>
-  </si>
-  <si>
     <t>Japan</t>
   </si>
   <si>
@@ -704,6 +692,102 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t>y = effect, x = causes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(how many data points) </t>
+  </si>
+  <si>
+    <t>R² Value</t>
+  </si>
+  <si>
+    <t>Interpretation</t>
+  </si>
+  <si>
+    <t>0.00–0.25</t>
+  </si>
+  <si>
+    <t>Weak explanatory power</t>
+  </si>
+  <si>
+    <t>0.25–0.50</t>
+  </si>
+  <si>
+    <t>Moderate explanatory power</t>
+  </si>
+  <si>
+    <t>0.50–0.70</t>
+  </si>
+  <si>
+    <t>Good explanatory power</t>
+  </si>
+  <si>
+    <t>0.70–0.90</t>
+  </si>
+  <si>
+    <t>Strong explanatory power</t>
+  </si>
+  <si>
+    <t>0.90–1.00</t>
+  </si>
+  <si>
+    <t>Very strong fit (but may indicate overfitting in some cases)</t>
+  </si>
+  <si>
+    <t>conclusion: cannot d</t>
+  </si>
+  <si>
+    <t>consider intercept</t>
+  </si>
+  <si>
+    <t>invalid, p &gt; 0.05</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>&lt; 0.001</t>
+  </si>
+  <si>
+    <t>Very strong evidence against the null hypothesis</t>
+  </si>
+  <si>
+    <t>&lt; 0.01</t>
+  </si>
+  <si>
+    <t>Strong evidence</t>
+  </si>
+  <si>
+    <t>&lt; 0.05</t>
+  </si>
+  <si>
+    <t>Statistically significant (most common threshold)</t>
+  </si>
+  <si>
+    <t>0.05–0.10</t>
+  </si>
+  <si>
+    <t>Marginally significant (sometimes acceptable in exploratory research)</t>
+  </si>
+  <si>
+    <t>&gt; 0.10</t>
+  </si>
+  <si>
+    <t>Not statistically significant</t>
+  </si>
+  <si>
+    <t>1) positive relationship with y</t>
+  </si>
+  <si>
+    <t>2) inverse relationship with y</t>
+  </si>
+  <si>
+    <t>x1, x2</t>
+  </si>
+  <si>
+    <t>none</t>
   </si>
 </sst>
 </file>
@@ -941,7 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="107">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1155,9 +1239,6 @@
     <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="11" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1202,15 +1283,39 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="11" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="1" builtinId="5"/>
+    <cellStyle name="Per cent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1228,7 +1333,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -2435,7 +2540,7 @@
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -3834,7 +3939,7 @@
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5079,7 +5184,7 @@
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -5715,7 +5820,7 @@
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -7052,7 +7157,7 @@
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -8396,7 +8501,7 @@
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -9317,7 +9422,7 @@
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="en-GB"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -15261,16 +15366,22 @@
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Data"/>
+      <sheetName val="moodle answers chart Country "/>
       <sheetName val="bangladesh"/>
+      <sheetName val="regression _bangladesh"/>
       <sheetName val="japan"/>
+      <sheetName val="Jpn rregression"/>
       <sheetName val="kaza"/>
+      <sheetName val="Kaza regression"/>
       <sheetName val="malaysia"/>
-      <sheetName val="mauritius"/>
+      <sheetName val="MAlaysia_regression"/>
       <sheetName val="pakistan"/>
-      <sheetName val="saudi"/>
+      <sheetName val="Pakistan _regression"/>
       <sheetName val="sg"/>
       <sheetName val="sg regression 2"/>
       <sheetName val="Sheet5"/>
+      <sheetName val="Sheet1"/>
+      <sheetName val="Sheet2"/>
       <sheetName val="chart A_sg"/>
       <sheetName val="spedning _SG"/>
       <sheetName val="chart 2 and 3"/>
@@ -15278,6 +15389,8 @@
       <sheetName val="regression 1_sg "/>
       <sheetName val="regression 3_sg"/>
       <sheetName val="Series - Metadata"/>
+      <sheetName val="mauritius"/>
+      <sheetName val="saudi"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -15292,7 +15405,13 @@
       <sheetData sheetId="9"/>
       <sheetData sheetId="10"/>
       <sheetData sheetId="11"/>
-      <sheetData sheetId="12">
+      <sheetData sheetId="12"/>
+      <sheetData sheetId="13"/>
+      <sheetData sheetId="14"/>
+      <sheetData sheetId="15"/>
+      <sheetData sheetId="16"/>
+      <sheetData sheetId="17"/>
+      <sheetData sheetId="18">
         <row r="1">
           <cell r="A1" t="str">
             <v>Time</v>
@@ -15736,7 +15855,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="13">
+      <sheetData sheetId="19">
         <row r="1">
           <cell r="O1" t="str">
             <v>Employment in agriculture (% of total employment) (modeled ILO estimate)</v>
@@ -15943,7 +16062,7 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="14">
+      <sheetData sheetId="20">
         <row r="1">
           <cell r="B1" t="str">
             <v>Manufacturing, value added (% of GDP)</v>
@@ -16228,9 +16347,11 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
+      <sheetData sheetId="21"/>
+      <sheetData sheetId="22"/>
+      <sheetData sheetId="23"/>
+      <sheetData sheetId="24"/>
+      <sheetData sheetId="25"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -16522,12 +16643,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U58"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="9" max="9" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="2" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" s="2" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -16552,8 +16673,8 @@
       <c r="H1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="I1" s="95" t="s">
-        <v>182</v>
+      <c r="I1" s="92" t="s">
+        <v>178</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>39</v>
@@ -16592,9 +16713,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B2">
         <v>2000</v>
@@ -16657,9 +16778,9 @@
         <v>19.212628471861752</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B3">
         <v>2001</v>
@@ -16722,9 +16843,9 @@
         <v>17.440346702441158</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B4">
         <v>2002</v>
@@ -16787,9 +16908,9 @@
         <v>17.254372894447737</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B5">
         <v>2003</v>
@@ -16852,9 +16973,9 @@
         <v>19.691763239399286</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B6">
         <v>2004</v>
@@ -16917,9 +17038,9 @@
         <v>20.372409545024979</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B7">
         <v>2005</v>
@@ -16982,9 +17103,9 @@
         <v>21.943308963938936</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B8">
         <v>2006</v>
@@ -17047,9 +17168,9 @@
         <v>21.793814847583047</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B9">
         <v>2007</v>
@@ -17112,9 +17233,9 @@
         <v>19.871043376318877</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B10">
         <v>2008</v>
@@ -17177,9 +17298,9 @@
         <v>22.330829704305092</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B11">
         <v>2009</v>
@@ -17242,9 +17363,9 @@
         <v>20.274613281485628</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B12">
         <v>2010</v>
@@ -17307,9 +17428,9 @@
         <v>15.915825251937466</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B13">
         <v>2011</v>
@@ -17372,9 +17493,9 @@
         <v>15.573199609973534</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B14">
         <v>2012</v>
@@ -17437,9 +17558,9 @@
         <v>10.758073085048988</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15">
         <v>2013</v>
@@ -17502,9 +17623,9 @@
         <v>8.5370905956525238</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B16">
         <v>2014</v>
@@ -17567,9 +17688,9 @@
         <v>9.2747660747096781</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B17">
         <v>2015</v>
@@ -17632,9 +17753,9 @@
         <v>7.5273093488910243</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B18">
         <v>2016</v>
@@ -17697,9 +17818,9 @@
         <v>6.6518808828017253</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B19">
         <v>2017</v>
@@ -17762,9 +17883,9 @@
         <v>6.868311645237851</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B20">
         <v>2018</v>
@@ -17827,9 +17948,9 @@
         <v>6.7073173372456951</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B21">
         <v>2019</v>
@@ -17892,9 +18013,9 @@
         <v>7.5269716577722159</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B22">
         <v>2020</v>
@@ -17957,9 +18078,9 @@
         <v>6.3676893732313804</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B23">
         <v>2021</v>
@@ -18022,9 +18143,9 @@
         <v>7.2301164079408027</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B24">
         <v>2022</v>
@@ -18087,9 +18208,9 @@
         <v>7.1909902112612683</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B25">
         <v>2023</v>
@@ -18152,9 +18273,9 @@
         <v>4.7644454890342285</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B26">
         <v>2024</v>
@@ -18217,9 +18338,9 @@
         <v>5.3195988044226183</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B27">
         <v>2025</v>
@@ -18282,9 +18403,9 @@
         <v>5.5391582744398056</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B28">
         <v>2000</v>
@@ -18347,9 +18468,9 @@
         <v>1.3445840850887789</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B29">
         <v>2001</v>
@@ -18412,9 +18533,9 @@
         <v>0.58542018264813089</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B30">
         <v>2002</v>
@@ -18477,9 +18598,9 @@
         <v>1.2449877045208144</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B31">
         <v>2003</v>
@@ -18542,9 +18663,9 @@
         <v>1.5865735164702106</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B32">
         <v>2004</v>
@@ -18607,9 +18728,9 @@
         <v>1.8891986126586391</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B33">
         <v>2005</v>
@@ -18672,9 +18793,9 @@
         <v>1.3877940814149701</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B34">
         <v>2006</v>
@@ -18737,9 +18858,9 @@
         <v>1.2835250459703347</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B35">
         <v>2007</v>
@@ -18802,9 +18923,9 @@
         <v>1.7424538320156908</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B36">
         <v>2008</v>
@@ -18867,9 +18988,9 @@
         <v>0.33636108306018836</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B37">
         <v>2009</v>
@@ -18932,9 +19053,9 @@
         <v>0.44390669128209076</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B38">
         <v>2010</v>
@@ -18997,9 +19118,9 @@
         <v>1.3254607170272608</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B39">
         <v>2011</v>
@@ -19062,9 +19183,9 @@
         <v>-0.64233291162983752</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B40">
         <v>2012</v>
@@ -19127,9 +19248,9 @@
         <v>-1.6264686310479837</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B41">
         <v>2013</v>
@@ -19192,9 +19313,9 @@
         <v>-2.3839512835696515</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B42">
         <v>2014</v>
@@ -19257,9 +19378,9 @@
         <v>-2.5485994733968478</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B43">
         <v>2015</v>
@@ -19322,9 +19443,9 @@
         <v>-0.54341063139738666</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B44">
         <v>2016</v>
@@ -19387,9 +19508,9 @@
         <v>0.78851291776939281</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B45">
         <v>2017</v>
@@ -19452,9 +19573,9 @@
         <v>0.74281699960539282</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B46">
         <v>2018</v>
@@ -19517,9 +19638,9 @@
         <v>1.8711999486957384E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B47">
         <v>2019</v>
@@ -19582,9 +19703,9 @@
         <v>-0.28270244369908964</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B48">
         <v>2020</v>
@@ -19647,9 +19768,9 @@
         <v>-0.26184209196454483</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B49">
         <v>2021</v>
@@ -19712,9 +19833,9 @@
         <v>-0.50142197413806322</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B50">
         <v>2022</v>
@@ -19777,9 +19898,9 @@
         <v>-3.5648963259740198</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B51">
         <v>2023</v>
@@ -19842,9 +19963,9 @@
         <v>-1.4764631115540887</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B52">
         <v>2024</v>
@@ -19904,9 +20025,9 @@
         <v>-0.89312011806516911</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B53">
         <v>2025</v>
@@ -19966,14 +20087,14 @@
         <v>167</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -19984,15 +20105,15 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F09706D3-3ACC-423F-8903-C5F506436891}">
   <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="8" customWidth="1"/>
     <col min="2" max="2" width="9" style="33"/>
-    <col min="3" max="3" width="13.28515625" style="20" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" style="20" customWidth="1"/>
     <col min="6" max="6" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="105" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="96" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>114</v>
       </c>
@@ -20009,7 +20130,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8">
         <v>2.2151140569329326E-2</v>
       </c>
@@ -20023,7 +20144,7 @@
         <v>11.921913382779238</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>3.9161122076016859E-2</v>
       </c>
@@ -20041,7 +20162,7 @@
       </c>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>-5.7913549410153149E-2</v>
       </c>
@@ -20061,7 +20182,7 @@
         <v>0.90255618496708157</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>-1.4434910115454443E-2</v>
       </c>
@@ -20069,7 +20190,7 @@
         <v>3.8314156675365557E-2</v>
       </c>
       <c r="C5" s="20">
-        <v>0.32201004028320313</v>
+        <v>0.32201004028320312</v>
       </c>
       <c r="D5">
         <v>-4.1502986226508227</v>
@@ -20081,7 +20202,7 @@
         <v>0.81460766702233278</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>8.6240329270084265E-2</v>
       </c>
@@ -20101,7 +20222,7 @@
         <v>0.77182482095056337</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>3.299476907418445E-2</v>
       </c>
@@ -20121,7 +20242,7 @@
         <v>1.9437792621639249E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8">
         <v>4.7335193758095443E-3</v>
       </c>
@@ -20141,7 +20262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>3.2000645038203282E-2</v>
       </c>
@@ -20155,7 +20276,7 @@
         <v>1.6712764155420388</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8">
         <v>1.0220811788075115E-2</v>
       </c>
@@ -20172,7 +20293,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>1.6540236975596098E-3</v>
       </c>
@@ -20202,7 +20323,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>2.9538255634357968E-2</v>
       </c>
@@ -20234,7 +20355,7 @@
         <v>4.8672019036150807E-5</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>4.8559426664513565E-2</v>
       </c>
@@ -20260,7 +20381,7 @@
         <v>3.7782778200185326E-4</v>
       </c>
     </row>
-    <row r="14" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8">
         <v>2.7682989319762721E-2</v>
       </c>
@@ -20286,7 +20407,7 @@
       <c r="J14" s="9"/>
       <c r="K14" s="9"/>
     </row>
-    <row r="15" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8">
         <v>-1.0909313190100821E-2</v>
       </c>
@@ -20300,7 +20421,7 @@
         <v>-1.4550979032228923</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>-2.1623002157920537E-2</v>
       </c>
@@ -20339,7 +20460,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>0.11857828176694038</v>
       </c>
@@ -20380,7 +20501,7 @@
         <v>1.2140787778921209E-2</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>7.9625886243627955E-3</v>
       </c>
@@ -20421,7 +20542,7 @@
         <v>0.42349155312422504</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="F19" t="s">
         <v>153</v>
       </c>
@@ -20450,7 +20571,7 @@
         <v>6.9061930286152835E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="F20" s="9" t="s">
         <v>71</v>
       </c>
@@ -20488,7 +20609,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{889850B5-D3B7-45EF-87FA-2DEE08221817}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20499,13 +20620,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="15.85546875" customWidth="1"/>
-    <col min="2" max="16" width="50.85546875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="16" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -20555,7 +20676,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -20602,7 +20723,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>22</v>
       </c>
@@ -20649,7 +20770,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>92</v>
       </c>
@@ -20693,7 +20814,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>59</v>
       </c>
@@ -20737,7 +20858,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -20781,7 +20902,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>35</v>
       </c>
@@ -20831,7 +20952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>95</v>
       </c>
@@ -20881,7 +21002,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>76</v>
       </c>
@@ -20931,7 +21052,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>64</v>
       </c>
@@ -20981,7 +21102,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -21031,7 +21152,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -21078,7 +21199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -21125,7 +21246,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -21180,37 +21301,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8A5EBE0-77D1-4DEE-BD25-B861D3CF253E}">
   <dimension ref="A1:AK28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="26" style="3" customWidth="1"/>
     <col min="4" max="4" width="9" style="3"/>
-    <col min="5" max="5" width="3.28515625" style="21" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" style="3" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+    <col min="5" max="5" width="3.33203125" style="21" customWidth="1"/>
+    <col min="6" max="6" width="25.6640625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" customWidth="1"/>
     <col min="8" max="8" width="5" style="22" customWidth="1"/>
-    <col min="9" max="9" width="19.5703125" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" customWidth="1"/>
-    <col min="11" max="11" width="17.42578125" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.42578125" style="6" customWidth="1"/>
-    <col min="13" max="13" width="10.42578125" style="59" customWidth="1"/>
-    <col min="14" max="14" width="12.140625" style="6" customWidth="1"/>
-    <col min="15" max="15" width="12.140625" style="66" customWidth="1"/>
-    <col min="16" max="16" width="18.28515625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="66" customWidth="1"/>
-    <col min="18" max="18" width="6.140625" style="24" customWidth="1"/>
-    <col min="19" max="19" width="13.28515625" customWidth="1"/>
-    <col min="20" max="20" width="13.28515625" style="99" customWidth="1"/>
-    <col min="21" max="21" width="4.42578125" style="22" customWidth="1"/>
-    <col min="22" max="22" width="13.28515625" customWidth="1"/>
+    <col min="9" max="9" width="19.5" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" customWidth="1"/>
+    <col min="11" max="11" width="17.5" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="6" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="59" customWidth="1"/>
+    <col min="14" max="14" width="12.1640625" style="6" customWidth="1"/>
+    <col min="15" max="15" width="12.1640625" style="66" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="6" customWidth="1"/>
+    <col min="17" max="17" width="17.83203125" style="66" customWidth="1"/>
+    <col min="18" max="18" width="6.1640625" style="24" customWidth="1"/>
+    <col min="19" max="19" width="13.33203125" customWidth="1"/>
+    <col min="20" max="20" width="13.33203125" style="96" customWidth="1"/>
+    <col min="21" max="21" width="4.5" style="22" customWidth="1"/>
+    <col min="22" max="22" width="13.33203125" customWidth="1"/>
     <col min="23" max="23" width="16" customWidth="1"/>
     <col min="24" max="24" width="30" style="50" customWidth="1"/>
     <col min="25" max="26" width="9" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="99" customWidth="1"/>
-    <col min="30" max="30" width="3.7109375" style="22" customWidth="1"/>
+    <col min="28" max="28" width="14.83203125" style="96" customWidth="1"/>
+    <col min="30" max="30" width="3.6640625" style="22" customWidth="1"/>
     <col min="32" max="32" width="9" style="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="2" customFormat="1" ht="151.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" s="2" customFormat="1" ht="151.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -21256,13 +21377,13 @@
         <v>110</v>
       </c>
       <c r="Q1" s="69" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="R1" s="30"/>
-      <c r="S1" s="96" t="s">
-        <v>182</v>
-      </c>
-      <c r="T1" s="97" t="s">
+      <c r="S1" s="93" t="s">
+        <v>178</v>
+      </c>
+      <c r="T1" s="94" t="s">
         <v>153</v>
       </c>
       <c r="U1" s="28"/>
@@ -21284,7 +21405,7 @@
       <c r="AA1" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="AB1" s="100" t="s">
+      <c r="AB1" s="97" t="s">
         <v>168</v>
       </c>
       <c r="AC1" s="27" t="s">
@@ -21310,7 +21431,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:37" s="18" customFormat="1" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" s="18" customFormat="1" ht="97" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="18" t="s">
         <v>106</v>
       </c>
@@ -21344,7 +21465,7 @@
       <c r="S2" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="T2" s="98" t="s">
+      <c r="T2" s="95" t="s">
         <v>151</v>
       </c>
       <c r="U2" s="25"/>
@@ -21356,7 +21477,7 @@
       <c r="Y2" s="55"/>
       <c r="Z2" s="55"/>
       <c r="AA2" s="55"/>
-      <c r="AB2" s="101" t="s">
+      <c r="AB2" s="98" t="s">
         <v>151</v>
       </c>
       <c r="AC2" s="55"/>
@@ -21380,9 +21501,9 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B3">
         <v>2000</v>
@@ -21445,7 +21566,7 @@
       <c r="AA3">
         <v>30.430790153344098</v>
       </c>
-      <c r="AB3" s="102"/>
+      <c r="AB3" s="99"/>
       <c r="AC3">
         <v>64.1185656445506</v>
       </c>
@@ -21466,9 +21587,9 @@
         <v>1.3445840850887789</v>
       </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B4">
         <v>2001</v>
@@ -21540,7 +21661,7 @@
       <c r="AA4">
         <v>29.651708418805299</v>
       </c>
-      <c r="AB4" s="99">
+      <c r="AB4" s="96">
         <f>M4-M3</f>
         <v>-0.57506237805308569</v>
       </c>
@@ -21567,9 +21688,9 @@
         <v>0.58542018264813089</v>
       </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B5">
         <v>2002</v>
@@ -21641,7 +21762,7 @@
       <c r="AA5">
         <v>28.789947213679</v>
       </c>
-      <c r="AB5" s="99">
+      <c r="AB5" s="96">
         <f t="shared" ref="AB5:AB27" si="7">M5-M4</f>
         <v>-0.63775574906170962</v>
       </c>
@@ -21668,9 +21789,9 @@
         <v>1.2449877045208144</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B6">
         <v>2003</v>
@@ -21742,7 +21863,7 @@
       <c r="AA6">
         <v>28.721289647208501</v>
       </c>
-      <c r="AB6" s="99">
+      <c r="AB6" s="96">
         <f t="shared" si="7"/>
         <v>0.951399925894576</v>
       </c>
@@ -21769,9 +21890,9 @@
         <v>1.5865735164702106</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B7">
         <v>2004</v>
@@ -21843,7 +21964,7 @@
       <c r="AA7">
         <v>27.822772205516198</v>
       </c>
-      <c r="AB7" s="99">
+      <c r="AB7" s="96">
         <f t="shared" si="7"/>
         <v>0.39140629627848489</v>
       </c>
@@ -21870,9 +21991,9 @@
         <v>1.8891986126586391</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B8">
         <v>2005</v>
@@ -21944,7 +22065,7 @@
       <c r="AA8">
         <v>27.392084976308698</v>
       </c>
-      <c r="AB8" s="99">
+      <c r="AB8" s="96">
         <f t="shared" si="7"/>
         <v>0.28258790508910614</v>
       </c>
@@ -21971,9 +22092,9 @@
         <v>1.3877940814149701</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B9">
         <v>2006</v>
@@ -22045,7 +22166,7 @@
       <c r="AA9">
         <v>27.495246318005801</v>
       </c>
-      <c r="AB9" s="99">
+      <c r="AB9" s="96">
         <f t="shared" si="7"/>
         <v>2.2879012433650925E-2</v>
       </c>
@@ -22072,9 +22193,9 @@
         <v>1.2835250459703347</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B10">
         <v>2007</v>
@@ -22146,7 +22267,7 @@
       <c r="AA10">
         <v>27.290260731194699</v>
       </c>
-      <c r="AB10" s="99">
+      <c r="AB10" s="96">
         <f t="shared" si="7"/>
         <v>3.7106879855957731E-2</v>
       </c>
@@ -22173,9 +22294,9 @@
         <v>1.7424538320156908</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B11">
         <v>2008</v>
@@ -22247,7 +22368,7 @@
       <c r="AA11">
         <v>26.771635935298701</v>
       </c>
-      <c r="AB11" s="99">
+      <c r="AB11" s="96">
         <f t="shared" si="7"/>
         <v>-0.86910502118931809</v>
       </c>
@@ -22274,9 +22395,9 @@
         <v>0.33636108306018836</v>
       </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B12">
         <v>2009</v>
@@ -22348,7 +22469,7 @@
       <c r="AA12">
         <v>26.094293020591699</v>
       </c>
-      <c r="AB12" s="99">
+      <c r="AB12" s="96">
         <f t="shared" si="7"/>
         <v>-1.1181954737153901</v>
       </c>
@@ -22375,9 +22496,9 @@
         <v>0.44390669128209076</v>
       </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B13">
         <v>2010</v>
@@ -22449,7 +22570,7 @@
       <c r="AA13">
         <v>25.519323328132199</v>
       </c>
-      <c r="AB13" s="99">
+      <c r="AB13" s="96">
         <f t="shared" si="7"/>
         <v>1.1193967097979134</v>
       </c>
@@ -22476,9 +22597,9 @@
         <v>1.3254607170272608</v>
       </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B14">
         <v>2011</v>
@@ -22550,7 +22671,7 @@
       <c r="AA14">
         <v>25.430185651152598</v>
       </c>
-      <c r="AB14" s="99">
+      <c r="AB14" s="96">
         <f t="shared" si="7"/>
         <v>0.3286594751730233</v>
       </c>
@@ -22577,9 +22698,9 @@
         <v>-0.64233291162983752</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B15">
         <v>2012</v>
@@ -22651,7 +22772,7 @@
       <c r="AA15">
         <v>25.311193891919999</v>
       </c>
-      <c r="AB15" s="99">
+      <c r="AB15" s="96">
         <f t="shared" si="7"/>
         <v>-0.18490803263721761</v>
       </c>
@@ -22678,9 +22799,9 @@
         <v>-1.6264686310479837</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B16">
         <v>2013</v>
@@ -22752,7 +22873,7 @@
       <c r="AA16">
         <v>25.1886060017838</v>
       </c>
-      <c r="AB16" s="99">
+      <c r="AB16" s="96">
         <f t="shared" si="7"/>
         <v>0.95994610606551145</v>
       </c>
@@ -22779,9 +22900,9 @@
         <v>-2.3839512835696515</v>
       </c>
     </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B17">
         <v>2014</v>
@@ -22835,7 +22956,7 @@
       <c r="S17">
         <v>62.833488464355497</v>
       </c>
-      <c r="T17" s="99">
+      <c r="T17" s="96">
         <f>S17-S16</f>
         <v>0.19121932983399859</v>
       </c>
@@ -22857,7 +22978,7 @@
       <c r="AA17">
         <v>25.125568425648702</v>
       </c>
-      <c r="AB17" s="99">
+      <c r="AB17" s="96">
         <f t="shared" si="7"/>
         <v>9.9890258511795227E-2</v>
       </c>
@@ -22884,9 +23005,9 @@
         <v>-2.5485994733968478</v>
       </c>
     </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B18">
         <v>2015</v>
@@ -22940,7 +23061,7 @@
       <c r="S18">
         <v>62.4498481750488</v>
       </c>
-      <c r="T18" s="99">
+      <c r="T18" s="96">
         <f t="shared" ref="T18:T26" si="9">S18-S17</f>
         <v>-0.38364028930669747</v>
       </c>
@@ -22962,7 +23083,7 @@
       <c r="AA18">
         <v>24.90449732946</v>
       </c>
-      <c r="AB18" s="99">
+      <c r="AB18" s="96">
         <f t="shared" si="7"/>
         <v>-0.46316764407036926</v>
       </c>
@@ -22989,9 +23110,9 @@
         <v>-0.54341063139738666</v>
       </c>
     </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B19">
         <v>2016</v>
@@ -23045,7 +23166,7 @@
       <c r="S19">
         <v>62.4975395202637</v>
       </c>
-      <c r="T19" s="99">
+      <c r="T19" s="96">
         <f t="shared" si="9"/>
         <v>4.7691345214900593E-2</v>
       </c>
@@ -23067,7 +23188,7 @@
       <c r="AA19">
         <v>24.594734051284</v>
       </c>
-      <c r="AB19" s="99">
+      <c r="AB19" s="96">
         <f t="shared" si="7"/>
         <v>0.82616306112364746</v>
       </c>
@@ -23094,9 +23215,9 @@
         <v>0.78851291776939281</v>
       </c>
     </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B20">
         <v>2017</v>
@@ -23150,7 +23271,7 @@
       <c r="S20">
         <v>63.287540435791001</v>
       </c>
-      <c r="T20" s="99">
+      <c r="T20" s="96">
         <f t="shared" si="9"/>
         <v>0.79000091552730112</v>
       </c>
@@ -23172,7 +23293,7 @@
       <c r="AA20">
         <v>24.581906234304501</v>
       </c>
-      <c r="AB20" s="99">
+      <c r="AB20" s="96">
         <f t="shared" si="7"/>
         <v>-3.4423707363241407E-2</v>
       </c>
@@ -23199,9 +23320,9 @@
         <v>0.74281699960539282</v>
       </c>
     </row>
-    <row r="21" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B21">
         <v>2018</v>
@@ -23255,7 +23376,7 @@
       <c r="S21">
         <v>62.605850219726598</v>
       </c>
-      <c r="T21" s="99">
+      <c r="T21" s="96">
         <f t="shared" si="9"/>
         <v>-0.68169021606440339</v>
       </c>
@@ -23277,7 +23398,7 @@
       <c r="AA21">
         <v>24.4484966180265</v>
       </c>
-      <c r="AB21" s="99">
+      <c r="AB21" s="96">
         <f t="shared" si="7"/>
         <v>0.89887603732049737</v>
       </c>
@@ -23304,9 +23425,9 @@
         <v>1.8711999486957384E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B22">
         <v>2019</v>
@@ -23360,7 +23481,7 @@
       <c r="S22">
         <v>62.400840759277301</v>
       </c>
-      <c r="T22" s="99">
+      <c r="T22" s="96">
         <f t="shared" si="9"/>
         <v>-0.20500946044929691</v>
       </c>
@@ -23382,7 +23503,7 @@
       <c r="AA22">
         <v>24.225756536984001</v>
       </c>
-      <c r="AB22" s="99">
+      <c r="AB22" s="96">
         <f t="shared" si="7"/>
         <v>-0.99913676686988651</v>
       </c>
@@ -23409,9 +23530,9 @@
         <v>-0.28270244369908964</v>
       </c>
     </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B23">
         <v>2020</v>
@@ -23465,7 +23586,7 @@
       <c r="S23">
         <v>62.298740386962898</v>
       </c>
-      <c r="T23" s="99">
+      <c r="T23" s="96">
         <f t="shared" si="9"/>
         <v>-0.10210037231440339</v>
       </c>
@@ -23487,7 +23608,7 @@
       <c r="AA23">
         <v>23.931926038039101</v>
       </c>
-      <c r="AB23" s="99">
+      <c r="AB23" s="96">
         <f t="shared" si="7"/>
         <v>-1.7306405438873615</v>
       </c>
@@ -23514,9 +23635,9 @@
         <v>-0.26184209196454483</v>
       </c>
     </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B24">
         <v>2021</v>
@@ -23570,7 +23691,7 @@
       <c r="S24">
         <v>62.041248321533203</v>
       </c>
-      <c r="T24" s="99">
+      <c r="T24" s="96">
         <f t="shared" si="9"/>
         <v>-0.25749206542969461</v>
       </c>
@@ -23592,7 +23713,7 @@
       <c r="AA24">
         <v>23.697096196032799</v>
       </c>
-      <c r="AB24" s="99">
+      <c r="AB24" s="96">
         <f t="shared" si="7"/>
         <v>0.60247937174166499</v>
       </c>
@@ -23619,9 +23740,9 @@
         <v>-0.50142197413806322</v>
       </c>
     </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B25">
         <v>2022</v>
@@ -23675,7 +23796,7 @@
       <c r="S25">
         <v>63.375228881835902</v>
       </c>
-      <c r="T25" s="99">
+      <c r="T25" s="96">
         <f t="shared" si="9"/>
         <v>1.3339805603026988</v>
       </c>
@@ -23697,7 +23818,7 @@
       <c r="AA25">
         <v>23.622131923842399</v>
       </c>
-      <c r="AB25" s="99">
+      <c r="AB25" s="96">
         <f t="shared" si="7"/>
         <v>0.7855573073249027</v>
       </c>
@@ -23721,9 +23842,9 @@
         <v>-3.5648963259740198</v>
       </c>
     </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B26">
         <v>2023</v>
@@ -23777,7 +23898,7 @@
       <c r="S26">
         <v>64.490760803222699</v>
       </c>
-      <c r="T26" s="99">
+      <c r="T26" s="96">
         <f t="shared" si="9"/>
         <v>1.1155319213867969</v>
       </c>
@@ -23799,7 +23920,7 @@
       <c r="AA26">
         <v>23.708847999943401</v>
       </c>
-      <c r="AB26" s="99">
+      <c r="AB26" s="96">
         <f t="shared" si="7"/>
         <v>-0.29382019316788272</v>
       </c>
@@ -23823,9 +23944,9 @@
         <v>-1.4764631115540887</v>
       </c>
     </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B27">
         <v>2024</v>
@@ -23897,7 +24018,7 @@
       <c r="AA27">
         <v>23.344843518808201</v>
       </c>
-      <c r="AB27" s="99">
+      <c r="AB27" s="96">
         <f t="shared" si="7"/>
         <v>0.14322788395289981</v>
       </c>
@@ -23921,7 +24042,7 @@
         <v>-0.89312011806516911</v>
       </c>
     </row>
-    <row r="28" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:37" s="15" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="15" t="s">
         <v>113</v>
       </c>
@@ -23936,18 +24057,18 @@
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="60"/>
-      <c r="N28" s="94">
+      <c r="N28" s="91">
         <f>AVERAGE(N3:N27)</f>
         <v>68028.140254514699</v>
       </c>
       <c r="O28" s="60"/>
-      <c r="P28" s="94">
+      <c r="P28" s="91">
         <f>AVERAGE(P3:P27)</f>
         <v>18374.506309445525</v>
       </c>
       <c r="Q28" s="70"/>
       <c r="R28" s="24"/>
-      <c r="T28" s="99"/>
+      <c r="T28" s="96"/>
       <c r="U28" s="22"/>
       <c r="V28" s="15">
         <f>AVERAGE(V3:V27)</f>
@@ -23969,7 +24090,7 @@
         <f>AVERAGE(AA3:AA27)</f>
         <v>25.923805694612593</v>
       </c>
-      <c r="AB28" s="99"/>
+      <c r="AB28" s="96"/>
       <c r="AC28" s="15">
         <f>AVERAGE(AC3:AC27)</f>
         <v>69.981175043331774</v>
@@ -24001,142 +24122,142 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C199883D-1A27-744D-8F46-B6D2A846FEA6}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="27"/>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
       <c r="D1" s="75"/>
       <c r="E1" s="75"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B4" s="52"/>
       <c r="C4" s="52"/>
       <c r="D4" s="52"/>
       <c r="E4" s="52"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B5" s="52"/>
       <c r="C5" s="52"/>
       <c r="D5" s="52"/>
       <c r="E5" s="52"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B6" s="52"/>
       <c r="C6" s="52"/>
       <c r="D6" s="52"/>
       <c r="E6" s="52"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B7" s="52"/>
       <c r="C7" s="52"/>
       <c r="D7" s="52"/>
       <c r="E7" s="52"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
       <c r="D8" s="52"/>
       <c r="E8" s="52"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="52"/>
       <c r="D9" s="52"/>
       <c r="E9" s="52"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B10" s="52"/>
       <c r="C10" s="52"/>
       <c r="D10" s="52"/>
       <c r="E10" s="52"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B11" s="52"/>
       <c r="C11" s="52"/>
       <c r="D11" s="52"/>
       <c r="E11" s="52"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B12" s="52"/>
       <c r="C12" s="52"/>
       <c r="D12" s="52"/>
       <c r="E12" s="52"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B13" s="52"/>
       <c r="C13" s="52"/>
       <c r="D13" s="52"/>
       <c r="E13" s="52"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B14" s="52"/>
       <c r="C14" s="52"/>
       <c r="D14" s="52"/>
       <c r="E14" s="52"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B15" s="52"/>
       <c r="C15" s="52"/>
       <c r="D15" s="52"/>
       <c r="E15" s="52"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B16" s="52"/>
       <c r="C16" s="52"/>
       <c r="D16" s="52"/>
       <c r="E16" s="52"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B17" s="52"/>
       <c r="C17" s="52"/>
       <c r="D17" s="52"/>
       <c r="E17" s="52"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B18" s="52"/>
       <c r="C18" s="52"/>
       <c r="D18" s="52"/>
       <c r="E18" s="52"/>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B19" s="52"/>
       <c r="C19" s="52"/>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B20" s="52"/>
       <c r="C20" s="52"/>
       <c r="D20" s="52"/>
       <c r="E20" s="52"/>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B21" s="52"/>
       <c r="C21" s="52"/>
       <c r="D21" s="52"/>
       <c r="E21" s="52"/>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B22" s="52"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
       <c r="E22" s="52"/>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B23" s="52"/>
       <c r="C23" s="52"/>
       <c r="D23" s="52"/>
       <c r="E23" s="52"/>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B24" s="52"/>
       <c r="C24" s="52"/>
       <c r="D24" s="52"/>
       <c r="E24" s="52"/>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B25" s="52"/>
       <c r="C25" s="52"/>
       <c r="D25" s="52"/>
@@ -24150,19 +24271,25 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E9EBE1-863F-494D-907B-2A4C46A41FF4}">
-  <dimension ref="A1:N27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="31.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.28515625" customWidth="1"/>
-    <col min="6" max="6" width="44.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.5703125" customWidth="1"/>
-    <col min="8" max="8" width="17.140625" customWidth="1"/>
-    <col min="9" max="9" width="10.5703125" customWidth="1"/>
+    <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5" customWidth="1"/>
+    <col min="3" max="3" width="31.1640625" customWidth="1"/>
+    <col min="4" max="4" width="16.33203125" customWidth="1"/>
+    <col min="6" max="6" width="44.33203125" customWidth="1"/>
+    <col min="7" max="7" width="16.5" customWidth="1"/>
+    <col min="8" max="8" width="17.1640625" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="105" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="112" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -24176,10 +24303,13 @@
         <v>73</v>
       </c>
       <c r="F1" s="76" t="s">
+        <v>179</v>
+      </c>
+      <c r="G1" s="27" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" ht="36.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="18" t="s">
         <v>106</v>
@@ -24188,13 +24318,13 @@
         <v>143</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F2" s="43" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -24208,7 +24338,7 @@
         <v>67813478</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -24226,7 +24356,7 @@
       </c>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -24246,7 +24376,7 @@
         <v>0.49890087598885879</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2003</v>
       </c>
@@ -24266,7 +24396,7 @@
         <v>0.24890208406245068</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2004</v>
       </c>
@@ -24286,7 +24416,7 @@
         <v>0.18062045534085527</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2005</v>
       </c>
@@ -24306,7 +24436,7 @@
         <v>208275691434.75491</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2006</v>
       </c>
@@ -24325,8 +24455,11 @@
       <c r="G9" s="38">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -24340,7 +24473,7 @@
         <v>66797225</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2008</v>
       </c>
@@ -24357,7 +24490,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2009</v>
       </c>
@@ -24387,7 +24520,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2010</v>
       </c>
@@ -24419,7 +24552,7 @@
         <v>4.2920238485684756E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2011</v>
       </c>
@@ -24445,7 +24578,7 @@
         <v>4.3378763642625235E+22</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2012</v>
       </c>
@@ -24471,7 +24604,7 @@
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
     </row>
-    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2013</v>
       </c>
@@ -24485,7 +24618,7 @@
         <v>65621150</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2014</v>
       </c>
@@ -24499,7 +24632,7 @@
         <v>65843453</v>
       </c>
       <c r="F17" s="10"/>
-      <c r="G17" s="103" t="s">
+      <c r="G17" s="100" t="s">
         <v>132</v>
       </c>
       <c r="H17" s="10" t="s">
@@ -24508,7 +24641,7 @@
       <c r="I17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="J17" s="103" t="s">
+      <c r="J17" s="100" t="s">
         <v>134</v>
       </c>
       <c r="K17" s="10" t="s">
@@ -24524,7 +24657,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2015</v>
       </c>
@@ -24565,7 +24698,7 @@
         <v>3953005945463.4873</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2016</v>
       </c>
@@ -24579,7 +24712,7 @@
         <v>66529155</v>
       </c>
       <c r="F19" t="s">
-        <v>173</v>
+        <v>80</v>
       </c>
       <c r="G19" s="37">
         <v>0.12492885422063238</v>
@@ -24606,7 +24739,7 @@
         <v>1.9362744175934659</v>
       </c>
     </row>
-    <row r="20" spans="1:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>2017</v>
       </c>
@@ -24620,7 +24753,7 @@
         <v>67070828</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="G20" s="38">
         <v>88098.975250276853</v>
@@ -24647,7 +24780,7 @@
         <v>192005.40856179368</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>2018</v>
       </c>
@@ -24661,7 +24794,7 @@
         <v>68187091</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2019</v>
       </c>
@@ -24675,7 +24808,7 @@
         <v>68812048</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2020</v>
       </c>
@@ -24688,8 +24821,14 @@
       <c r="D23">
         <v>68656452</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F23" t="s">
+        <v>211</v>
+      </c>
+      <c r="G23" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2021</v>
       </c>
@@ -24702,8 +24841,14 @@
       <c r="D24">
         <v>68592854</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>212</v>
+      </c>
+      <c r="G24" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2022</v>
       </c>
@@ -24717,7 +24862,7 @@
         <v>68931266</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -24731,7 +24876,7 @@
         <v>69197135</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -24744,6 +24889,124 @@
       <c r="D27">
         <v>69501768</v>
       </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F29" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F30" t="s">
+        <v>198</v>
+      </c>
+      <c r="G30" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B34" s="104"/>
+      <c r="C34" s="104"/>
+      <c r="F34" s="104" t="s">
+        <v>185</v>
+      </c>
+      <c r="G34" s="104" t="s">
+        <v>186</v>
+      </c>
+      <c r="J34" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="K34" s="104" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F35" t="s">
+        <v>187</v>
+      </c>
+      <c r="G35" t="s">
+        <v>188</v>
+      </c>
+      <c r="J35" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="K35" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="36" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F36" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" t="s">
+        <v>190</v>
+      </c>
+      <c r="J36" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="K36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F37" t="s">
+        <v>191</v>
+      </c>
+      <c r="G37" t="s">
+        <v>192</v>
+      </c>
+      <c r="J37" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="K37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="38" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F38" t="s">
+        <v>193</v>
+      </c>
+      <c r="G38" t="s">
+        <v>194</v>
+      </c>
+      <c r="J38" s="104" t="s">
+        <v>207</v>
+      </c>
+      <c r="K38" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="39" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="F39" t="s">
+        <v>195</v>
+      </c>
+      <c r="G39" t="s">
+        <v>196</v>
+      </c>
+      <c r="J39" s="104" t="s">
+        <v>209</v>
+      </c>
+      <c r="K39" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="42" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B42" s="104"/>
+      <c r="C42" s="104"/>
+    </row>
+    <row r="43" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B43" s="104"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B44" s="104"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B45" s="104"/>
+    </row>
+    <row r="46" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B46" s="104"/>
+    </row>
+    <row r="47" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B47" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24752,15 +25015,16 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B438CE9C-62C9-41DF-BCF2-4EBD77C1ABFB}">
-  <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P50"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="9.140625" customWidth="1"/>
-    <col min="8" max="8" width="60.5703125" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="5" max="5" width="8.83203125" style="111"/>
+    <col min="6" max="6" width="9.1640625" style="111" customWidth="1"/>
+    <col min="8" max="8" width="60.5" customWidth="1"/>
+    <col min="13" max="13" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="112" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -24773,34 +25037,37 @@
       <c r="D1" s="56" t="s">
         <v>148</v>
       </c>
-      <c r="E1" s="31" t="s">
+      <c r="E1" s="94" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="31" t="s">
+      <c r="F1" s="94" t="s">
         <v>152</v>
       </c>
       <c r="H1" s="76" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="I1" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="96" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="18"/>
       <c r="C2" s="18"/>
       <c r="D2" s="57" t="s">
         <v>149</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="H2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2000</v>
       </c>
@@ -24811,10 +25078,10 @@
         <v>1.1736681231453474</v>
       </c>
       <c r="D3" s="58"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="E3" s="96"/>
+      <c r="F3" s="99"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -24827,8 +25094,8 @@
       <c r="D4" s="59">
         <v>-0.57506237805308569</v>
       </c>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20">
+      <c r="E4" s="96"/>
+      <c r="F4" s="96">
         <v>-9.863794426466007E-4</v>
       </c>
       <c r="H4" s="11" t="s">
@@ -24836,7 +25103,7 @@
       </c>
       <c r="I4" s="11"/>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -24849,18 +25116,18 @@
       <c r="D5" s="59">
         <v>-1.2128181271147953</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20">
+      <c r="E5" s="96"/>
+      <c r="F5" s="96">
         <v>2.3539550617580028E-4</v>
       </c>
       <c r="H5" t="s">
         <v>117</v>
       </c>
       <c r="I5">
-        <v>0.90240610352795714</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.97685917487482732</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2003</v>
       </c>
@@ -24873,18 +25140,18 @@
       <c r="D6" s="59">
         <v>-0.2614182012202193</v>
       </c>
-      <c r="E6" s="20"/>
-      <c r="F6" s="20">
+      <c r="E6" s="96"/>
+      <c r="F6" s="96">
         <v>1.0296995830918008E-3</v>
       </c>
       <c r="H6" t="s">
         <v>118</v>
       </c>
-      <c r="I6">
-        <v>0.81433677568451002</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I6" s="37">
+        <v>0.9542538475371285</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2004</v>
       </c>
@@ -24897,18 +25164,18 @@
       <c r="D7" s="59">
         <v>0.12998809505826556</v>
       </c>
-      <c r="E7" s="20"/>
-      <c r="F7" s="20">
+      <c r="E7" s="96"/>
+      <c r="F7" s="96">
         <v>-8.1913267857269996E-4</v>
       </c>
       <c r="H7" t="s">
         <v>119</v>
       </c>
       <c r="I7">
-        <v>0.5667858099305233</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+        <v>0.86276154261138549</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2005</v>
       </c>
@@ -24921,18 +25188,18 @@
       <c r="D8" s="59">
         <v>0.41257600014737172</v>
       </c>
-      <c r="E8" s="20"/>
-      <c r="F8" s="20">
+      <c r="E8" s="96"/>
+      <c r="F8" s="96">
         <v>3.5077821749244977E-3</v>
       </c>
       <c r="H8" t="s">
         <v>120</v>
       </c>
       <c r="I8">
-        <v>1.4948070101490698</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.90744908435851745</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2006</v>
       </c>
@@ -24945,18 +25212,18 @@
       <c r="D9" s="59">
         <v>0.43545501258102265</v>
       </c>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20">
+      <c r="E9" s="96"/>
+      <c r="F9" s="96">
         <v>2.3615081122094032E-3</v>
       </c>
       <c r="H9" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="I9" s="9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="I9" s="38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -24969,12 +25236,12 @@
       <c r="D10" s="59">
         <v>0.47256189243698038</v>
       </c>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20">
+      <c r="E10" s="96"/>
+      <c r="F10" s="96">
         <v>3.3667852588522978E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2008</v>
       </c>
@@ -24987,15 +25254,15 @@
       <c r="D11" s="59">
         <v>-0.39654312875233766</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="20">
+      <c r="E11" s="96"/>
+      <c r="F11" s="96">
         <v>1.2981778852562999E-3</v>
       </c>
       <c r="H11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2009</v>
       </c>
@@ -25008,8 +25275,8 @@
       <c r="D12" s="59">
         <v>-1.5147386024677276</v>
       </c>
-      <c r="E12" s="20"/>
-      <c r="F12" s="20">
+      <c r="E12" s="96"/>
+      <c r="F12" s="96">
         <v>-4.5235162930808009E-3</v>
       </c>
       <c r="H12" s="10"/>
@@ -25029,7 +25296,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2010</v>
       </c>
@@ -25042,8 +25309,8 @@
       <c r="D13" s="59">
         <v>-0.39534189266981412</v>
       </c>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20">
+      <c r="E13" s="96"/>
+      <c r="F13" s="96">
         <v>6.4791566104050249E-4</v>
       </c>
       <c r="H13" t="s">
@@ -25053,19 +25320,19 @@
         <v>4</v>
       </c>
       <c r="J13">
-        <v>29.401512084603937</v>
+        <v>34.354519276191056</v>
       </c>
       <c r="K13">
-        <v>7.3503780211509842</v>
+        <v>8.5886298190477639</v>
       </c>
       <c r="L13">
-        <v>3.2895722026541754</v>
+        <v>10.429880942573497</v>
       </c>
       <c r="M13">
-        <v>0.17771994065381636</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>8.9399594460586554E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2011</v>
       </c>
@@ -25078,24 +25345,24 @@
       <c r="D14" s="59">
         <v>-6.6682417496790825E-2</v>
       </c>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20">
+      <c r="E14" s="96"/>
+      <c r="F14" s="96">
         <v>1.580088361309899E-3</v>
       </c>
       <c r="H14" t="s">
         <v>124</v>
       </c>
       <c r="I14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J14">
-        <v>6.7033439927724041</v>
+        <v>1.6469276814062235</v>
       </c>
       <c r="K14">
-        <v>2.2344479975908014</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.82346384070311174</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2012</v>
       </c>
@@ -25108,24 +25375,24 @@
       <c r="D15" s="59">
         <v>-0.25159045013400844</v>
       </c>
-      <c r="E15" s="20"/>
-      <c r="F15" s="20">
+      <c r="E15" s="96"/>
+      <c r="F15" s="96">
         <v>-1.5867996142118999E-3</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>125</v>
       </c>
       <c r="I15" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J15" s="9">
-        <v>36.10485607737634</v>
+        <v>36.001446957597281</v>
       </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
     </row>
-    <row r="16" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2013</v>
       </c>
@@ -25138,13 +25405,13 @@
       <c r="D16" s="59">
         <v>0.70835565593150296</v>
       </c>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20">
+      <c r="E16" s="96"/>
+      <c r="F16" s="96">
         <v>3.122515945531399E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" s="105">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A17">
         <v>2014</v>
       </c>
       <c r="B17" s="77">
@@ -25156,15 +25423,15 @@
       <c r="D17" s="79">
         <v>0.80824591444329819</v>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="105">
         <f>D17-D16</f>
         <v>9.9890258511795227E-2</v>
       </c>
-      <c r="F17" s="85">
+      <c r="F17" s="106">
         <v>4.8581973539594016E-3</v>
       </c>
       <c r="H17" s="10"/>
-      <c r="I17" s="10" t="s">
+      <c r="I17" s="100" t="s">
         <v>132</v>
       </c>
       <c r="J17" s="10" t="s">
@@ -25173,7 +25440,7 @@
       <c r="K17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="L17" s="10" t="s">
+      <c r="L17" s="100" t="s">
         <v>134</v>
       </c>
       <c r="M17" s="10" t="s">
@@ -25189,269 +25456,269 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" s="105">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A18">
         <v>2015</v>
       </c>
       <c r="B18" s="80">
         <v>1.7999773578347487</v>
       </c>
-      <c r="C18" s="104">
+      <c r="C18" s="81">
         <v>2.8541342380652424</v>
       </c>
-      <c r="D18" s="106">
+      <c r="D18" s="101">
         <v>0.34507827037292893</v>
       </c>
-      <c r="E18" s="104">
+      <c r="E18" s="107">
         <f t="shared" ref="E18:E26" si="0">D18-D17</f>
         <v>-0.46316764407036926</v>
       </c>
-      <c r="F18" s="86">
+      <c r="F18" s="108">
         <v>8.9782830654430018E-4</v>
       </c>
       <c r="H18" t="s">
         <v>126</v>
       </c>
-      <c r="I18">
-        <v>0.51976821824539432</v>
+      <c r="I18" s="37">
+        <v>0.77434510527699452</v>
       </c>
       <c r="J18">
-        <v>2.0690763107560475</v>
+        <v>1.2602638555583723</v>
       </c>
       <c r="K18">
-        <v>0.25120785325480299</v>
-      </c>
-      <c r="L18">
-        <v>0.81787736246532439</v>
+        <v>0.61443093988751529</v>
+      </c>
+      <c r="L18" s="37">
+        <v>0.60151636007434317</v>
       </c>
       <c r="M18">
-        <v>-6.0649560422702367</v>
+        <v>-4.6481326130458198</v>
       </c>
       <c r="N18">
-        <v>7.1044924787610251</v>
+        <v>6.1968228235998088</v>
       </c>
       <c r="O18">
-        <v>-6.0649560422702367</v>
+        <v>-4.6481326130458198</v>
       </c>
       <c r="P18">
-        <v>7.1044924787610251</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" s="105">
+        <v>6.1968228235998088</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A19">
         <v>2016</v>
       </c>
       <c r="B19" s="80">
         <v>0.70498649511125677</v>
       </c>
-      <c r="C19" s="104">
+      <c r="C19" s="81">
         <v>0.65911104198646342</v>
       </c>
-      <c r="D19" s="106">
+      <c r="D19" s="101">
         <v>1.1712413314965764</v>
       </c>
-      <c r="E19" s="104">
+      <c r="E19" s="107">
         <f t="shared" si="0"/>
         <v>0.82616306112364746</v>
       </c>
-      <c r="F19" s="86">
+      <c r="F19" s="108">
         <v>-3.7918470149631012E-3</v>
       </c>
-      <c r="H19" t="s">
-        <v>173</v>
-      </c>
-      <c r="I19">
-        <v>0.63355793003556715</v>
+      <c r="H19" s="102" t="s">
+        <v>40</v>
+      </c>
+      <c r="I19" s="37">
+        <v>0.96540727849653285</v>
       </c>
       <c r="J19">
-        <v>0.34069866378136121</v>
+        <v>0.24639752908387261</v>
       </c>
       <c r="K19">
-        <v>1.8595844286672767</v>
-      </c>
-      <c r="L19">
-        <v>0.15989586087999388</v>
+        <v>3.9180883107310405</v>
+      </c>
+      <c r="L19" s="37">
+        <v>5.9396134378704502E-2</v>
       </c>
       <c r="M19">
-        <v>-0.45069727373052237</v>
+        <v>-9.4755722619714489E-2</v>
       </c>
       <c r="N19">
-        <v>1.7178131338016567</v>
+        <v>2.0255702796127801</v>
       </c>
       <c r="O19">
-        <v>-0.45069727373052237</v>
+        <v>-9.4755722619714489E-2</v>
       </c>
       <c r="P19">
-        <v>1.7178131338016567</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="105">
+        <v>2.0255702796127801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A20">
         <v>2017</v>
       </c>
       <c r="B20" s="80">
         <v>1.6234506224544134</v>
       </c>
-      <c r="C20" s="104">
+      <c r="C20" s="81">
         <v>1.6097468891013165</v>
       </c>
-      <c r="D20" s="106">
+      <c r="D20" s="101">
         <v>1.136817624133335</v>
       </c>
-      <c r="E20" s="104">
+      <c r="E20" s="107">
         <f t="shared" si="0"/>
         <v>-3.4423707363241407E-2</v>
       </c>
-      <c r="F20" s="86">
+      <c r="F20" s="108">
         <v>1.3269004203637198E-2</v>
       </c>
-      <c r="H20" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20">
-        <v>-0.7215490387092357</v>
+      <c r="H20" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="I20" s="37">
+        <v>-1.1285642548534036</v>
       </c>
       <c r="J20">
-        <v>2.4735121457415716</v>
+        <v>1.5105460898904508</v>
       </c>
       <c r="K20">
-        <v>-0.29171032774246258</v>
-      </c>
-      <c r="L20">
-        <v>0.78951644040308522</v>
+        <v>-0.74712334989742046</v>
+      </c>
+      <c r="L20" s="37">
+        <v>0.53288304514736762</v>
       </c>
       <c r="M20">
-        <v>-8.5933686279988795</v>
+        <v>-7.6279195119329302</v>
       </c>
       <c r="N20">
-        <v>7.1502705505804087</v>
+        <v>5.3707910022261229</v>
       </c>
       <c r="O20">
-        <v>-8.5933686279988795</v>
+        <v>-7.6279195119329302</v>
       </c>
       <c r="P20">
-        <v>7.1502705505804087</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="105">
+        <v>5.3707910022261229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" ht="16" x14ac:dyDescent="0.2">
+      <c r="A21">
         <v>2018</v>
       </c>
       <c r="B21" s="80">
         <v>0.83414384596558477</v>
       </c>
-      <c r="C21" s="104">
+      <c r="C21" s="81">
         <v>1.2789260829120224</v>
       </c>
-      <c r="D21" s="106">
+      <c r="D21" s="101">
         <v>2.0356936614538323</v>
       </c>
-      <c r="E21" s="104">
+      <c r="E21" s="107">
         <f t="shared" si="0"/>
         <v>0.89887603732049737</v>
       </c>
-      <c r="F21" s="86">
+      <c r="F21" s="108">
         <v>-1.6904672173859991E-3</v>
       </c>
-      <c r="H21" t="s">
-        <v>175</v>
-      </c>
-      <c r="I21">
-        <v>1.365373930351818</v>
+      <c r="H21" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="I21" s="37">
+        <v>1.3672159408410824</v>
       </c>
       <c r="J21">
-        <v>2.6972512658689975</v>
+        <v>1.6374143465351416</v>
       </c>
       <c r="K21">
-        <v>0.50620939458968917</v>
-      </c>
-      <c r="L21">
-        <v>0.64756608448099051</v>
+        <v>0.83498470850349282</v>
+      </c>
+      <c r="L21" s="37">
+        <v>0.49158074514130079</v>
       </c>
       <c r="M21">
-        <v>-7.21848339513478</v>
+        <v>-5.6780093670092793</v>
       </c>
       <c r="N21">
-        <v>9.9492312558384164</v>
+        <v>8.4124412486914437</v>
       </c>
       <c r="O21">
-        <v>-7.21848339513478</v>
+        <v>-5.6780093670092793</v>
       </c>
       <c r="P21">
-        <v>9.9492312558384164</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="105">
+        <v>8.4124412486914437</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>2019</v>
       </c>
       <c r="B22" s="80">
         <v>-0.30849692114325933</v>
       </c>
-      <c r="C22" s="104">
+      <c r="C22" s="81">
         <v>1.6606576436665677</v>
       </c>
-      <c r="D22" s="106">
+      <c r="D22" s="101">
         <v>1.0365568945839458</v>
       </c>
-      <c r="E22" s="104">
+      <c r="E22" s="107">
         <f t="shared" si="0"/>
         <v>-0.99913676686988651</v>
       </c>
-      <c r="F22" s="86">
+      <c r="F22" s="108">
         <v>5.6473259349969503E-2</v>
       </c>
-      <c r="H22" s="9" t="s">
-        <v>176</v>
-      </c>
-      <c r="I22" s="9">
-        <v>-9.7249540505499183</v>
+      <c r="H22" s="114" t="s">
+        <v>152</v>
+      </c>
+      <c r="I22" s="38">
+        <v>-7.1438378821707769</v>
       </c>
       <c r="J22" s="9">
-        <v>70.391542602380653</v>
+        <v>42.745126327960506</v>
       </c>
       <c r="K22" s="9">
-        <v>-0.13815514891445238</v>
-      </c>
-      <c r="L22" s="9">
-        <v>0.89886974356454474</v>
+        <v>-0.1671263719601605</v>
+      </c>
+      <c r="L22" s="38">
+        <v>0.88264046653799122</v>
       </c>
       <c r="M22" s="9">
-        <v>-233.74225872871702</v>
+        <v>-191.06127236065572</v>
       </c>
       <c r="N22" s="9">
-        <v>214.2923506276172</v>
+        <v>176.77359659631415</v>
       </c>
       <c r="O22" s="9">
-        <v>-233.74225872871702</v>
+        <v>-191.06127236065572</v>
       </c>
       <c r="P22" s="9">
-        <v>214.2923506276172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" s="105">
+        <v>176.77359659631415</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A23">
         <v>2020</v>
       </c>
       <c r="B23" s="80">
         <v>-4.2832794267557261</v>
       </c>
-      <c r="C23" s="104">
+      <c r="C23" s="81">
         <v>-3.45000520130327</v>
       </c>
-      <c r="D23" s="106">
+      <c r="D23" s="101">
         <v>-0.6940836493034156</v>
       </c>
-      <c r="E23" s="104">
+      <c r="E23" s="107">
         <f t="shared" si="0"/>
         <v>-1.7306405438873615</v>
       </c>
-      <c r="F23" s="86">
+      <c r="F23" s="108">
         <v>3.768539613590402E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="105">
+    <row r="24" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24">
         <v>2021</v>
       </c>
       <c r="B24" s="82">
@@ -25463,15 +25730,15 @@
       <c r="D24" s="84">
         <v>-9.1604277561750574E-2</v>
       </c>
-      <c r="E24" s="83">
+      <c r="E24" s="109">
         <f t="shared" si="0"/>
         <v>0.60247937174166499</v>
       </c>
-      <c r="F24" s="87">
+      <c r="F24" s="110">
         <v>-4.9692738437576101E-2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2022</v>
       </c>
@@ -25484,13 +25751,13 @@
       <c r="D25" s="59">
         <v>0.6939530297631521</v>
       </c>
-      <c r="E25" s="20">
+      <c r="E25" s="96">
         <f t="shared" si="0"/>
         <v>0.7855573073249027</v>
       </c>
-      <c r="F25" s="37"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F25" s="99"/>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2023</v>
       </c>
@@ -25503,13 +25770,14 @@
       <c r="D26" s="59">
         <v>0.40013283659526938</v>
       </c>
-      <c r="E26" s="20">
+      <c r="E26" s="96">
         <f t="shared" si="0"/>
         <v>-0.29382019316788272</v>
       </c>
-      <c r="F26" s="37"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="F26" s="99"/>
+      <c r="H26" s="104"/>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -25522,8 +25790,59 @@
       <c r="D27" s="59">
         <v>0.5433607205481692</v>
       </c>
-      <c r="E27" s="20"/>
-      <c r="F27" s="37"/>
+      <c r="E27" s="96"/>
+      <c r="F27" s="99"/>
+      <c r="H27" s="104"/>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H28" s="104"/>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H29" s="104"/>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H30" s="104"/>
+    </row>
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H31" s="104"/>
+    </row>
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="H32" s="104"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H33" s="104"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H34" s="104"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H35" s="104"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="H36" s="104"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="104"/>
+      <c r="C37" s="104"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="104"/>
+      <c r="C45" s="104"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="104"/>
+    </row>
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="104"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="104"/>
+    </row>
+    <row r="49" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B49" s="104"/>
+    </row>
+    <row r="50" spans="2:2" x14ac:dyDescent="0.2">
+      <c r="B50" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25532,18 +25851,18 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{07465A97-DC41-4842-AB21-460AF263DB7D}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:O45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="19.7109375" customWidth="1"/>
-    <col min="7" max="7" width="46.85546875" customWidth="1"/>
-    <col min="12" max="12" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="13.5" customWidth="1"/>
+    <col min="3" max="3" width="12.1640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="111" customWidth="1"/>
+    <col min="5" max="5" width="19.6640625" style="111" customWidth="1"/>
+    <col min="7" max="7" width="46.83203125" customWidth="1"/>
+    <col min="12" max="12" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="112" x14ac:dyDescent="0.2">
       <c r="A1" s="27" t="s">
         <v>74</v>
       </c>
@@ -25551,19 +25870,22 @@
         <v>141</v>
       </c>
       <c r="C1" s="69" t="s">
+        <v>177</v>
+      </c>
+      <c r="D1" s="94" t="s">
+        <v>153</v>
+      </c>
+      <c r="E1" s="112" t="s">
+        <v>71</v>
+      </c>
+      <c r="G1" s="76" t="s">
         <v>181</v>
       </c>
-      <c r="D1" s="31" t="s">
-        <v>153</v>
-      </c>
-      <c r="E1" s="27" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="76" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="75" x14ac:dyDescent="0.25">
+      <c r="H1" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="64" x14ac:dyDescent="0.2">
       <c r="A2" s="18"/>
       <c r="B2" s="65" t="s">
         <v>142</v>
@@ -25571,26 +25893,26 @@
       <c r="C2" s="68" t="s">
         <v>145</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="95" t="s">
         <v>151</v>
       </c>
-      <c r="E2" s="55"/>
-      <c r="G2" s="43" t="s">
+      <c r="E2" s="113"/>
+      <c r="G2" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2000</v>
       </c>
       <c r="B3" s="62"/>
       <c r="C3" s="62"/>
-      <c r="D3" s="20"/>
-      <c r="E3">
+      <c r="D3" s="96"/>
+      <c r="E3" s="111">
         <v>5.9527340709045689</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2001</v>
       </c>
@@ -25600,8 +25922,8 @@
       <c r="C4" s="66">
         <v>-0.93019454533183632</v>
       </c>
-      <c r="D4" s="20"/>
-      <c r="E4">
+      <c r="D4" s="96"/>
+      <c r="E4" s="111">
         <v>-3.8993064419592969</v>
       </c>
       <c r="G4" s="11" t="s">
@@ -25609,7 +25931,7 @@
       </c>
       <c r="H4" s="11"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>2002</v>
       </c>
@@ -25619,18 +25941,18 @@
       <c r="C5" s="66">
         <v>-3.2380649204662029</v>
       </c>
-      <c r="D5" s="20"/>
-      <c r="E5">
+      <c r="D5" s="96"/>
+      <c r="E5" s="111">
         <v>-2.021784916640712</v>
       </c>
       <c r="G5" t="s">
         <v>117</v>
       </c>
       <c r="H5">
-        <v>0.87250112639139465</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.90939026701511216</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>2003</v>
       </c>
@@ -25640,18 +25962,18 @@
       <c r="C6" s="66">
         <v>-0.72907516487515189</v>
       </c>
-      <c r="D6" s="20"/>
-      <c r="E6">
+      <c r="D6" s="96"/>
+      <c r="E6" s="111">
         <v>3.6892235030364589</v>
       </c>
       <c r="G6" t="s">
         <v>118</v>
       </c>
       <c r="H6" s="37">
-        <v>0.76125821555425244</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.82699065774181701</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>2004</v>
       </c>
@@ -25661,18 +25983,18 @@
       <c r="C7" s="66">
         <v>9.3201215593103209E-2</v>
       </c>
-      <c r="D7" s="20"/>
-      <c r="E7">
+      <c r="D7" s="96"/>
+      <c r="E7" s="111">
         <v>5.2725079432044453</v>
       </c>
       <c r="G7" t="s">
         <v>119</v>
       </c>
       <c r="H7">
-        <v>0.64188732333137866</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>0.72318505238690722</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>2005</v>
       </c>
@@ -25682,18 +26004,18 @@
       <c r="C8" s="66">
         <v>2.4537738050092481</v>
       </c>
-      <c r="D8" s="20"/>
-      <c r="E8">
+      <c r="D8" s="96"/>
+      <c r="E8" s="111">
         <v>3.6194835541111843</v>
       </c>
       <c r="G8" t="s">
         <v>120</v>
       </c>
       <c r="H8">
-        <v>1.1401461141028588</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.0630657226795186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2006</v>
       </c>
@@ -25703,18 +26025,18 @@
       <c r="C9" s="66">
         <v>0.30008532136144822</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9">
+      <c r="D9" s="96"/>
+      <c r="E9" s="111">
         <v>3.9753848633023949</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>121</v>
       </c>
       <c r="H9" s="38">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>2007</v>
       </c>
@@ -25724,12 +26046,12 @@
       <c r="C10" s="66">
         <v>-1.5598376214867455</v>
       </c>
-      <c r="D10" s="20"/>
-      <c r="E10">
+      <c r="D10" s="96"/>
+      <c r="E10" s="111">
         <v>5.4347531277969949</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>2008</v>
       </c>
@@ -25739,15 +26061,15 @@
       <c r="C11" s="66">
         <v>-3.2920040222025904</v>
       </c>
-      <c r="D11" s="20"/>
-      <c r="E11">
+      <c r="D11" s="96"/>
+      <c r="E11" s="111">
         <v>0.21369602246103625</v>
       </c>
       <c r="G11" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>2009</v>
       </c>
@@ -25757,8 +26079,8 @@
       <c r="C12" s="66">
         <v>-9.1025998784664353</v>
       </c>
-      <c r="D12" s="20"/>
-      <c r="E12">
+      <c r="D12" s="96"/>
+      <c r="E12" s="111">
         <v>-17.167772289390797</v>
       </c>
       <c r="G12" s="10"/>
@@ -25778,7 +26100,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>2010</v>
       </c>
@@ -25788,8 +26110,8 @@
       <c r="C13" s="66">
         <v>-1.1987277173142665</v>
       </c>
-      <c r="D13" s="20"/>
-      <c r="E13">
+      <c r="D13" s="96"/>
+      <c r="E13" s="111">
         <v>16.886878489115944</v>
       </c>
       <c r="G13" t="s">
@@ -25799,19 +26121,19 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>24.870002571948461</v>
+        <v>27.009794683704023</v>
       </c>
       <c r="J13">
-        <v>8.2900008573161532</v>
+        <v>9.0032648945680069</v>
       </c>
       <c r="K13">
-        <v>6.3772516178645136</v>
+        <v>7.9667244838498732</v>
       </c>
       <c r="L13">
-        <v>2.6960101617431578E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>2.3739194872037739E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>2011</v>
       </c>
@@ -25821,24 +26143,24 @@
       <c r="C14" s="66">
         <v>1.5034484451759154</v>
       </c>
-      <c r="D14" s="20"/>
-      <c r="E14">
+      <c r="D14" s="96"/>
+      <c r="E14" s="111">
         <v>-3.1910773685471412</v>
       </c>
       <c r="G14" t="s">
         <v>124</v>
       </c>
       <c r="H14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14">
-        <v>7.7995989690230934</v>
+        <v>5.6505436536806348</v>
       </c>
       <c r="J14">
-        <v>1.299933161503849</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>1.1301087307361271</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>2012</v>
       </c>
@@ -25848,24 +26170,24 @@
       <c r="C15" s="66">
         <v>3.6936688947658212</v>
       </c>
-      <c r="D15" s="20"/>
-      <c r="E15">
+      <c r="D15" s="96"/>
+      <c r="E15" s="111">
         <v>2.0336463223787291</v>
       </c>
       <c r="G15" s="9" t="s">
         <v>125</v>
       </c>
       <c r="H15" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I15" s="9">
-        <v>32.669601540971556</v>
+        <v>32.660338337384658</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
     </row>
-    <row r="16" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>2013</v>
       </c>
@@ -25875,30 +26197,30 @@
       <c r="C16" s="66">
         <v>2.7465999616935024</v>
       </c>
-      <c r="D16" s="20"/>
-      <c r="E16">
+      <c r="D16" s="96"/>
+      <c r="E16" s="111">
         <v>-1.4564912307609745</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>2014</v>
       </c>
-      <c r="B17" s="88">
+      <c r="B17" s="85">
         <v>9.6886490521281607E-2</v>
       </c>
-      <c r="C17" s="89">
+      <c r="C17" s="86">
         <v>3.2307540889096353</v>
       </c>
-      <c r="D17" s="78">
+      <c r="D17" s="105">
         <f>C17-C16</f>
         <v>0.48415412721613293</v>
       </c>
-      <c r="E17" s="85">
+      <c r="E17" s="106">
         <v>2.9031184885573822</v>
       </c>
       <c r="G17" s="10"/>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="100" t="s">
         <v>132</v>
       </c>
       <c r="I17" s="10" t="s">
@@ -25907,7 +26229,7 @@
       <c r="J17" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="K17" s="10" t="s">
+      <c r="K17" s="100" t="s">
         <v>134</v>
       </c>
       <c r="L17" s="10" t="s">
@@ -25923,277 +26245,277 @@
         <v>138</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>2015</v>
       </c>
-      <c r="B18" s="90">
+      <c r="B18" s="87">
         <v>1.4498958120713157</v>
       </c>
-      <c r="C18" s="91">
+      <c r="C18" s="88">
         <v>2.5004275356005334</v>
       </c>
-      <c r="D18" s="81">
+      <c r="D18" s="107">
         <f t="shared" ref="D18:D26" si="0">C18-C17</f>
         <v>-0.7303265533091019</v>
       </c>
-      <c r="E18" s="86">
+      <c r="E18" s="108">
         <v>2.0940745404323167</v>
       </c>
       <c r="G18" t="s">
         <v>126</v>
       </c>
-      <c r="H18">
-        <v>-0.5035750489208316</v>
+      <c r="H18" s="37">
+        <v>-0.45001622799412272</v>
       </c>
       <c r="I18">
-        <v>0.42524554601217013</v>
+        <v>0.39839421601631153</v>
       </c>
       <c r="J18">
-        <v>-1.1841982911830893</v>
-      </c>
-      <c r="K18">
-        <v>0.28111524658666631</v>
+        <v>-1.1295752044143572</v>
+      </c>
+      <c r="K18" s="37">
+        <v>0.30991409672664633</v>
       </c>
       <c r="L18">
-        <v>-1.5441134151046243</v>
+        <v>-1.4741211631082234</v>
       </c>
       <c r="M18">
-        <v>0.53696331726296098</v>
+        <v>0.57408870711997795</v>
       </c>
       <c r="N18">
-        <v>-1.5441134151046243</v>
+        <v>-1.4741211631082234</v>
       </c>
       <c r="O18">
-        <v>0.53696331726296098</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.57408870711997795</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>2016</v>
       </c>
-      <c r="B19" s="90">
+      <c r="B19" s="87">
         <v>-0.46085708769510181</v>
       </c>
-      <c r="C19" s="91">
+      <c r="C19" s="88">
         <v>-0.50620144891972196</v>
       </c>
-      <c r="D19" s="81">
+      <c r="D19" s="107">
         <f t="shared" si="0"/>
         <v>-3.0066289845202556</v>
       </c>
-      <c r="E19" s="86">
+      <c r="E19" s="108">
         <v>0.86648629529422294</v>
       </c>
-      <c r="G19" t="s">
-        <v>173</v>
-      </c>
-      <c r="H19">
-        <v>0.21462761453424245</v>
+      <c r="G19" s="115" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="37">
+        <v>0.50363399598329939</v>
       </c>
       <c r="I19">
-        <v>0.28631741219953466</v>
+        <v>0.3393973645692443</v>
       </c>
       <c r="J19">
-        <v>0.74961425812506444</v>
-      </c>
-      <c r="K19">
-        <v>0.48183362661814588</v>
+        <v>1.4839066196713124</v>
+      </c>
+      <c r="K19" s="37">
+        <v>0.19795173658728349</v>
       </c>
       <c r="L19">
-        <v>-0.48596585456595826</v>
+        <v>-0.36881470444123626</v>
       </c>
       <c r="M19">
-        <v>0.91522108363444321</v>
+        <v>1.376082696407835</v>
       </c>
       <c r="N19">
-        <v>-0.48596585456595826</v>
+        <v>-0.36881470444123626</v>
       </c>
       <c r="O19">
-        <v>0.91522108363444321</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+        <v>1.376082696407835</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" ht="16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>2017</v>
       </c>
-      <c r="B20" s="90">
+      <c r="B20" s="87">
         <v>0.48116305194575515</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="88">
         <v>0.46761335394750919</v>
       </c>
-      <c r="D20" s="81">
+      <c r="D20" s="107">
         <f t="shared" si="0"/>
         <v>0.9738148028672311</v>
       </c>
-      <c r="E20" s="86">
+      <c r="E20" s="108">
         <v>4.2332505930130964</v>
       </c>
-      <c r="G20" t="s">
-        <v>174</v>
-      </c>
-      <c r="H20">
-        <v>0.24449531397220281</v>
+      <c r="G20" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="H20" s="37">
+        <v>0.14855835836693254</v>
       </c>
       <c r="I20">
-        <v>0.2230286071702785</v>
+        <v>0.21927936991341646</v>
       </c>
       <c r="J20">
-        <v>1.0962509118192845</v>
-      </c>
-      <c r="K20">
-        <v>0.31500788667642005</v>
+        <v>0.6774844274023204</v>
+      </c>
+      <c r="K20" s="37">
+        <v>0.5281731864188407</v>
       </c>
       <c r="L20">
-        <v>-0.30123602805710759</v>
+        <v>-0.4151172068622721</v>
       </c>
       <c r="M20">
-        <v>0.79022665600151321</v>
+        <v>0.71223392359613713</v>
       </c>
       <c r="N20">
-        <v>-0.30123602805710759</v>
+        <v>-0.4151172068622721</v>
       </c>
       <c r="O20">
-        <v>0.79022665600151321</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.71223392359613713</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>2018</v>
       </c>
-      <c r="B21" s="90">
+      <c r="B21" s="87">
         <v>-1.177577936084699</v>
       </c>
-      <c r="C21" s="91">
+      <c r="C21" s="88">
         <v>-0.74166946034856995</v>
       </c>
-      <c r="D21" s="81">
+      <c r="D21" s="107">
         <f t="shared" si="0"/>
         <v>-1.2092828142960792</v>
       </c>
-      <c r="E21" s="86">
+      <c r="E21" s="108">
         <v>3.7499108296410242</v>
       </c>
-      <c r="G21" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="H21" s="9">
-        <v>0.29974237268679343</v>
+      <c r="G21" s="114" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="38">
+        <v>0.28760467547050844</v>
       </c>
       <c r="I21" s="9">
-        <v>0.13329959186617352</v>
+        <v>0.12459905220056462</v>
       </c>
       <c r="J21" s="9">
-        <v>2.2486368374459884</v>
-      </c>
-      <c r="K21" s="9">
-        <v>6.5563928894571702E-2</v>
+        <v>2.308241277851431</v>
+      </c>
+      <c r="K21" s="38">
+        <v>6.9058590368606648E-2</v>
       </c>
       <c r="L21" s="9">
-        <v>-2.6429978403334164E-2</v>
+        <v>-3.2687384853764004E-2</v>
       </c>
       <c r="M21" s="9">
-        <v>0.62591472377692103</v>
+        <v>0.60789673579478087</v>
       </c>
       <c r="N21" s="9">
-        <v>-2.6429978403334164E-2</v>
+        <v>-3.2687384853764004E-2</v>
       </c>
       <c r="O21" s="9">
-        <v>0.62591472377692103</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+        <v>0.60789673579478087</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>2019</v>
       </c>
-      <c r="B22" s="90">
+      <c r="B22" s="87">
         <v>-1.3312546043414482</v>
       </c>
-      <c r="C22" s="91">
+      <c r="C22" s="88">
         <v>0.61769795830808505</v>
       </c>
-      <c r="D22" s="81">
+      <c r="D22" s="107">
         <f t="shared" si="0"/>
         <v>1.3593674186566549</v>
       </c>
-      <c r="E22" s="86">
+      <c r="E22" s="108">
         <v>-0.88808077103949756</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2020</v>
       </c>
-      <c r="B23" s="90">
+      <c r="B23" s="87">
         <v>-3.6142819172798877</v>
       </c>
-      <c r="C23" s="91">
+      <c r="C23" s="88">
         <v>-2.7751836479383445</v>
       </c>
-      <c r="D23" s="81">
+      <c r="D23" s="107">
         <f t="shared" si="0"/>
         <v>-3.3928816062464295</v>
       </c>
-      <c r="E23" s="86">
+      <c r="E23" s="108">
         <v>-6.1172472387425643</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2021</v>
       </c>
-      <c r="B24" s="90">
+      <c r="B24" s="87">
         <v>3.6591515316319545</v>
       </c>
-      <c r="C24" s="91">
+      <c r="C24" s="88">
         <v>1.1326298434793314</v>
       </c>
-      <c r="D24" s="81">
+      <c r="D24" s="107">
         <f t="shared" si="0"/>
         <v>3.9078134914176759</v>
       </c>
-      <c r="E24" s="86">
+      <c r="E24" s="108">
         <v>6.2091300540067209</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2022</v>
       </c>
-      <c r="B25" s="90">
+      <c r="B25" s="87">
         <v>0.63329967449560209</v>
       </c>
-      <c r="C25" s="91">
+      <c r="C25" s="88">
         <v>-0.22334416663875237</v>
       </c>
-      <c r="D25" s="81">
+      <c r="D25" s="107">
         <f t="shared" si="0"/>
         <v>-1.3559740101180837</v>
       </c>
-      <c r="E25" s="86">
+      <c r="E25" s="108">
         <v>2.4197275090146064</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>2023</v>
       </c>
-      <c r="B26" s="92">
+      <c r="B26" s="89">
         <v>0.3193745457253746</v>
       </c>
-      <c r="C26" s="93">
+      <c r="C26" s="90">
         <v>1.5075004155496978</v>
       </c>
-      <c r="D26" s="83">
+      <c r="D26" s="109">
         <f t="shared" si="0"/>
         <v>1.7308445821884502</v>
       </c>
-      <c r="E26" s="87">
+      <c r="E26" s="110">
         <v>-1.2039654711156373</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2024</v>
       </c>
@@ -26203,9 +26525,105 @@
       <c r="C27" s="66">
         <v>-1.1032122677168328</v>
       </c>
-      <c r="D27" s="20"/>
-      <c r="E27">
+      <c r="D27" s="96"/>
+      <c r="E27" s="111">
         <v>-5.7836044198951271</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="B32" s="104" t="s">
+        <v>185</v>
+      </c>
+      <c r="C32" s="104" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B33" t="s">
+        <v>187</v>
+      </c>
+      <c r="C33" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C34" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B35" t="s">
+        <v>191</v>
+      </c>
+      <c r="C35" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
+      <c r="C36" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B37" t="s">
+        <v>195</v>
+      </c>
+      <c r="C37" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B40" s="104" t="s">
+        <v>200</v>
+      </c>
+      <c r="C40" s="104" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B41" s="104" t="s">
+        <v>201</v>
+      </c>
+      <c r="C41" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B42" s="104" t="s">
+        <v>203</v>
+      </c>
+      <c r="C42" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B43" s="104" t="s">
+        <v>205</v>
+      </c>
+      <c r="C43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B44" s="104" t="s">
+        <v>207</v>
+      </c>
+      <c r="C44" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.2">
+      <c r="B45" s="104" t="s">
+        <v>209</v>
+      </c>
+      <c r="C45" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -26216,30 +26634,30 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1524E039-9D98-4AD9-9E87-88901946F8BA}">
   <dimension ref="A1:AG29"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="9" style="3"/>
-    <col min="3" max="3" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="43"/>
-    <col min="9" max="9" width="17.42578125" style="6" customWidth="1"/>
+    <col min="9" max="9" width="17.5" style="6" customWidth="1"/>
     <col min="10" max="10" width="19" style="6" customWidth="1"/>
     <col min="11" max="11" width="9" style="63"/>
-    <col min="12" max="12" width="12.140625" style="6" customWidth="1"/>
-    <col min="13" max="13" width="16.28515625" style="66" customWidth="1"/>
-    <col min="14" max="14" width="11.42578125" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.1640625" style="6" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" style="66" customWidth="1"/>
+    <col min="14" max="14" width="11.5" style="6" customWidth="1"/>
     <col min="15" max="15" width="9" style="63"/>
     <col min="16" max="16" width="9" style="40"/>
-    <col min="17" max="17" width="15.42578125" customWidth="1"/>
-    <col min="18" max="18" width="13.28515625" style="20" customWidth="1"/>
-    <col min="21" max="21" width="9.28515625" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="20" customWidth="1"/>
+    <col min="17" max="17" width="15.5" customWidth="1"/>
+    <col min="18" max="18" width="13.33203125" style="20" customWidth="1"/>
+    <col min="21" max="21" width="9.33203125" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" style="20" customWidth="1"/>
     <col min="28" max="28" width="12" style="73" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="5.42578125" customWidth="1"/>
+    <col min="29" max="29" width="5.5" customWidth="1"/>
     <col min="30" max="33" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" s="2" customFormat="1" ht="151.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" s="2" customFormat="1" ht="151.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -26335,7 +26753,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="2" spans="1:33" s="47" customFormat="1" ht="113.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" s="47" customFormat="1" ht="121" thickBot="1" x14ac:dyDescent="0.25">
       <c r="C2" s="47" t="s">
         <v>106</v>
       </c>
@@ -26389,7 +26807,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="3" spans="1:33" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -26476,7 +26894,7 @@
         <v>12.337260101284532</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -26578,7 +26996,7 @@
         <v>16.496255724564534</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -26680,7 +27098,7 @@
         <v>18.426222147387328</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>75</v>
       </c>
@@ -26782,7 +27200,7 @@
         <v>27.953848478026121</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -26884,7 +27302,7 @@
         <v>26.379678346782697</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>75</v>
       </c>
@@ -26986,7 +27404,7 @@
         <v>29.88882255327351</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>75</v>
       </c>
@@ -27091,7 +27509,7 @@
         <v>30.711834579105247</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>75</v>
       </c>
@@ -27196,7 +27614,7 @@
         <v>31.270315543664491</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -27301,7 +27719,7 @@
         <v>20.660826979180964</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>75</v>
       </c>
@@ -27359,7 +27777,7 @@
       </c>
       <c r="R12" s="20">
         <f t="shared" si="9"/>
-        <v>0.32201004028320313</v>
+        <v>0.32201004028320312</v>
       </c>
       <c r="S12">
         <v>20.273376429073512</v>
@@ -27406,7 +27824,7 @@
         <v>23.497058193413821</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>75</v>
       </c>
@@ -27511,7 +27929,7 @@
         <v>26.312365798407917</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>75</v>
       </c>
@@ -27616,7 +28034,7 @@
         <v>27.556785921536942</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>75</v>
       </c>
@@ -27721,7 +28139,7 @@
         <v>24.226259963852854</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -27826,7 +28244,7 @@
         <v>23.113812627266899</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>75</v>
       </c>
@@ -27931,7 +28349,7 @@
         <v>23.439752408773177</v>
       </c>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>75</v>
       </c>
@@ -28036,7 +28454,7 @@
         <v>27.297818059101541</v>
       </c>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>75</v>
       </c>
@@ -28141,7 +28559,7 @@
         <v>26.253769658413212</v>
       </c>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>75</v>
       </c>
@@ -28246,7 +28664,7 @@
         <v>26.545597667222111</v>
       </c>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>75</v>
       </c>
@@ -28351,7 +28769,7 @@
         <v>29.700268952184881</v>
       </c>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>75</v>
       </c>
@@ -28456,7 +28874,7 @@
         <v>29.367995967723893</v>
       </c>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -28561,7 +28979,7 @@
         <v>31.279400415186071</v>
       </c>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -28666,7 +29084,7 @@
         <v>35.785344863952751</v>
       </c>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -28771,7 +29189,7 @@
         <v>39.774395154749833</v>
       </c>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -28873,7 +29291,7 @@
         <v>37.158805824026295</v>
       </c>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>75</v>
       </c>
@@ -28975,7 +29393,7 @@
         <v>36.012331849548822</v>
       </c>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33" x14ac:dyDescent="0.2">
       <c r="I29" s="1"/>
       <c r="J29" s="1"/>
       <c r="L29" s="1"/>
@@ -28990,22 +29408,22 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0722AECA-F9D8-4E94-9029-29AE891E1F4A}">
   <dimension ref="A1:M28"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="80" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>43</v>
       </c>
@@ -29019,7 +29437,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>140533304238.72125</v>
       </c>
@@ -29030,7 +29448,7 @@
         <v>2058990.2999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>139028385430.87299</v>
       </c>
@@ -29045,7 +29463,7 @@
       </c>
       <c r="F3" s="11"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>144482970559.8894</v>
       </c>
@@ -29062,7 +29480,7 @@
         <v>0.98087740551070124</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>151054425108.65015</v>
       </c>
@@ -29079,7 +29497,7 @@
         <v>0.96212048464140454</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>166069208808.39377</v>
       </c>
@@ -29096,7 +29514,7 @@
         <v>0.95867689233607767</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>178302402123.90665</v>
       </c>
@@ -29113,7 +29531,7 @@
         <v>17652168151.839451</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>194361682395.94128</v>
       </c>
@@ -29130,7 +29548,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>211896059498.4816</v>
       </c>
@@ -29141,7 +29559,7 @@
         <v>2431366.5179999997</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>215844707508.2283</v>
       </c>
@@ -29155,7 +29573,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>216120888113.03256</v>
       </c>
@@ -29182,7 +29600,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>247501100140.01782</v>
       </c>
@@ -29211,7 +29629,7 @@
         <v>2.3038200450523506E-16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>262883130580.25568</v>
       </c>
@@ -29234,7 +29652,7 @@
         <v>3.1159904046081507E+20</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>274543305511.61057</v>
       </c>
@@ -29257,7 +29675,7 @@
       <c r="I14" s="9"/>
       <c r="J14" s="9"/>
     </row>
-    <row r="15" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>287769788882.22137</v>
       </c>
@@ -29268,7 +29686,7 @@
         <v>3056622.2830000003</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>299095084828.97827</v>
       </c>
@@ -29304,7 +29722,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>307998545269.39795</v>
       </c>
@@ -29342,7 +29760,7 @@
         <v>-19897117643.188736</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>319541032495.04486</v>
       </c>
@@ -29380,7 +29798,7 @@
         <v>3.6960153322484635</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>333846562289.74597</v>
       </c>
@@ -29418,7 +29836,7 @@
         <v>167381.23715056467</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>345370865382.86688</v>
       </c>
@@ -29429,7 +29847,7 @@
         <v>3267785.3281200002</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>349888458531.08569</v>
       </c>
@@ -29440,7 +29858,7 @@
         <v>3347043.2490000003</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>336541232520.5025</v>
       </c>
@@ -29451,7 +29869,7 @@
         <v>3290514.0870000003</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>369376902514.86536</v>
       </c>
@@ -29462,7 +29880,7 @@
         <v>3228708.4160000002</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>384550906479.00623</v>
       </c>
@@ -29473,7 +29891,7 @@
         <v>3334790.2022700002</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>391555143381.88489</v>
       </c>
@@ -29484,7 +29902,7 @@
         <v>3497684.1319599999</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>408736675576.89142</v>
       </c>
@@ -29495,7 +29913,7 @@
         <v>3588444.4651200003</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1"/>
     </row>
   </sheetData>
@@ -29507,16 +29925,16 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7E65112-9F7A-4E65-AF87-66BF12EAFA09}">
   <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="5" max="5" width="9" style="33"/>
-    <col min="6" max="6" width="13.28515625" style="20" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="20" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" style="20" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="20" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="120" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="96" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>28</v>
       </c>
@@ -29542,7 +29960,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>75</v>
       </c>
@@ -29556,7 +29974,7 @@
         <v>11.414764762166143</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>75</v>
       </c>
@@ -29580,7 +29998,7 @@
       </c>
       <c r="J3" s="11"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>75</v>
       </c>
@@ -29606,7 +30024,7 @@
         <v>0.82393292350564329</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>75</v>
       </c>
@@ -29632,7 +30050,7 @@
         <v>0.67886546243655621</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>75</v>
       </c>
@@ -29658,7 +30076,7 @@
         <v>0.55041164741117865</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>75</v>
       </c>
@@ -29684,7 +30102,7 @@
         <v>2.8961175812830007</v>
       </c>
     </row>
-    <row r="8" spans="1:17" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" s="34" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
         <v>75</v>
       </c>
@@ -29720,7 +30138,7 @@
       <c r="P8"/>
       <c r="Q8"/>
     </row>
-    <row r="9" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="34" t="s">
         <v>75</v>
       </c>
@@ -29752,7 +30170,7 @@
       <c r="P9"/>
       <c r="Q9"/>
     </row>
-    <row r="10" spans="1:17" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" s="34" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
         <v>75</v>
       </c>
@@ -29786,7 +30204,7 @@
       <c r="P10"/>
       <c r="Q10"/>
     </row>
-    <row r="11" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="34" t="s">
         <v>75</v>
       </c>
@@ -29803,7 +30221,7 @@
         <v>1.5944602852234029E-2</v>
       </c>
       <c r="F11" s="34">
-        <v>0.32201004028320313</v>
+        <v>0.32201004028320312</v>
       </c>
       <c r="G11" s="34">
         <v>-1.8600894741257219E-2</v>
@@ -29828,7 +30246,7 @@
       <c r="P11"/>
       <c r="Q11"/>
     </row>
-    <row r="12" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="34" t="s">
         <v>75</v>
       </c>
@@ -29872,7 +30290,7 @@
       <c r="P12"/>
       <c r="Q12"/>
     </row>
-    <row r="13" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="34" t="s">
         <v>75</v>
       </c>
@@ -29912,7 +30330,7 @@
       <c r="P13"/>
       <c r="Q13"/>
     </row>
-    <row r="14" spans="1:17" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" s="34" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
         <v>75</v>
       </c>
@@ -29950,7 +30368,7 @@
       <c r="P14"/>
       <c r="Q14"/>
     </row>
-    <row r="15" spans="1:17" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="34" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
         <v>75</v>
       </c>
@@ -29982,7 +30400,7 @@
       <c r="P15"/>
       <c r="Q15"/>
     </row>
-    <row r="16" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="34" t="s">
         <v>75</v>
       </c>
@@ -30030,7 +30448,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="17" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
         <v>75</v>
       </c>
@@ -30080,7 +30498,7 @@
         <v>3.6188667293148882</v>
       </c>
     </row>
-    <row r="18" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="34" t="s">
         <v>75</v>
       </c>
@@ -30130,7 +30548,7 @@
         <v>0.46286742114136015</v>
       </c>
     </row>
-    <row r="19" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="34" t="s">
         <v>75</v>
       </c>
@@ -30180,7 +30598,7 @@
         <v>64.721430858297609</v>
       </c>
     </row>
-    <row r="20" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="34" t="s">
         <v>75</v>
       </c>
@@ -30230,7 +30648,7 @@
         <v>2.896543407993434</v>
       </c>
     </row>
-    <row r="21" spans="1:17" s="34" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="34" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
         <v>75</v>
       </c>
@@ -30280,7 +30698,7 @@
         <v>63.08826787265825</v>
       </c>
     </row>
-    <row r="22" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="34" t="s">
         <v>75</v>
       </c>
@@ -30312,7 +30730,7 @@
       <c r="P22"/>
       <c r="Q22"/>
     </row>
-    <row r="23" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" s="34" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="34" t="s">
         <v>75</v>
       </c>
@@ -30344,7 +30762,7 @@
       <c r="P23"/>
       <c r="Q23"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>75</v>
       </c>
@@ -30364,7 +30782,7 @@
         <v>1.2494697570800994</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>75</v>
       </c>
@@ -30381,7 +30799,7 @@
         <v>4.8846829878268612E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>75</v>
       </c>
@@ -30398,7 +30816,7 @@
         <v>2.5948693402780471E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>113</v>
       </c>
@@ -30409,17 +30827,17 @@
         <v>4.0059049215621823</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>157</v>
       </c>
